--- a/docs/M2_PV_Performance_Workbook.xlsx
+++ b/docs/M2_PV_Performance_Workbook.xlsx
@@ -75,7 +75,7 @@
     <definedName name="rstr_fleet_mean">M2b_PeerZScore!$B$15</definedName>
     <definedName name="rstr_fleet_median">M2b_PeerZScore!$B$16</definedName>
     <definedName name="rstr_fleet_std">M2b_PeerZScore!$B$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Findings_Summary'!$A$4:$H$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Findings_Summary'!$A$4:$H$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5636,22 +5636,10 @@
         <f>IFERROR((B10-rstr_fleet_median)/rstr_fleet_std,"")</f>
         <v/>
       </c>
-      <c r="D26" s="15">
-        <f>IF(cfg_stat_method="median",C26,IF(cfg_stat_method="mean",B26,IF(ABS(B26)&gt;=ABS(C26),B26,C26)))</f>
-        <v/>
-      </c>
-      <c r="E26" s="5">
-        <f>IF(ABS(D26)&gt;cfg_z_threshold,1,0)</f>
-        <v/>
-      </c>
-      <c r="F26" s="5">
-        <f>IFERROR(IF(E10&gt;cfg_voc_ratio_threshold,1,0),0)</f>
-        <v/>
-      </c>
-      <c r="G26" s="5">
-        <f>IF(AND(E26=1,F26=1),1,0)</f>
-        <v/>
-      </c>
+      <c r="D26" s="15" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5">
         <f>IF(G26=1,"high_R","")</f>
         <v/>
@@ -6452,7 +6440,7 @@
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>Note: window 15 butuh ≥15 samples. Dummy 24 timestep cukup untuk demo.</t>
+          <t>Note: rolling_MAD pakai AVEDEV (mean-abs-dev) = proxy MAD universal-compatible (MEDIAN(IF()) array gagal tanpa CSE di LibreOffice). True Hampel = median-abs-dev x 1.4826; AVEDEV strict ~1.2533. Demo mekanisme, bukan filter produksi (preprocessing.py pakai pvanalytics).</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6504,7 @@
         <v/>
       </c>
       <c r="E6" s="15">
-        <f>MEDIAN(IF(B6:B6&gt;0,ABS(B6:B6-C6)))</f>
+        <f>AVEDEV(B6:B6)</f>
         <v/>
       </c>
       <c r="F6" s="15">
@@ -6550,7 +6538,7 @@
         <v/>
       </c>
       <c r="E7" s="15">
-        <f>MEDIAN(IF(B6:B7&gt;0,ABS(B6:B7-C7)))</f>
+        <f>AVEDEV(B6:B7)</f>
         <v/>
       </c>
       <c r="F7" s="15">
@@ -6584,7 +6572,7 @@
         <v/>
       </c>
       <c r="E8" s="15">
-        <f>MEDIAN(IF(B6:B8&gt;0,ABS(B6:B8-C8)))</f>
+        <f>AVEDEV(B6:B8)</f>
         <v/>
       </c>
       <c r="F8" s="15">
@@ -6618,7 +6606,7 @@
         <v/>
       </c>
       <c r="E9" s="15">
-        <f>MEDIAN(IF(B6:B9&gt;0,ABS(B6:B9-C9)))</f>
+        <f>AVEDEV(B6:B9)</f>
         <v/>
       </c>
       <c r="F9" s="15">
@@ -6652,7 +6640,7 @@
         <v/>
       </c>
       <c r="E10" s="15">
-        <f>MEDIAN(IF(B6:B10&gt;0,ABS(B6:B10-C10)))</f>
+        <f>AVEDEV(B6:B10)</f>
         <v/>
       </c>
       <c r="F10" s="15">
@@ -6686,7 +6674,7 @@
         <v/>
       </c>
       <c r="E11" s="15">
-        <f>MEDIAN(IF(B6:B11&gt;0,ABS(B6:B11-C11)))</f>
+        <f>AVEDEV(B6:B11)</f>
         <v/>
       </c>
       <c r="F11" s="15">
@@ -6720,7 +6708,7 @@
         <v/>
       </c>
       <c r="E12" s="15">
-        <f>MEDIAN(IF(B6:B12&gt;0,ABS(B6:B12-C12)))</f>
+        <f>AVEDEV(B6:B12)</f>
         <v/>
       </c>
       <c r="F12" s="15">
@@ -6754,7 +6742,7 @@
         <v/>
       </c>
       <c r="E13" s="15">
-        <f>MEDIAN(IF(B6:B13&gt;0,ABS(B6:B13-C13)))</f>
+        <f>AVEDEV(B6:B13)</f>
         <v/>
       </c>
       <c r="F13" s="15">
@@ -6788,7 +6776,7 @@
         <v/>
       </c>
       <c r="E14" s="15">
-        <f>MEDIAN(IF(B6:B14&gt;0,ABS(B6:B14-C14)))</f>
+        <f>AVEDEV(B6:B14)</f>
         <v/>
       </c>
       <c r="F14" s="15">
@@ -6822,7 +6810,7 @@
         <v/>
       </c>
       <c r="E15" s="15">
-        <f>MEDIAN(IF(B6:B15&gt;0,ABS(B6:B15-C15)))</f>
+        <f>AVEDEV(B6:B15)</f>
         <v/>
       </c>
       <c r="F15" s="15">
@@ -6856,7 +6844,7 @@
         <v/>
       </c>
       <c r="E16" s="15">
-        <f>MEDIAN(IF(B6:B16&gt;0,ABS(B6:B16-C16)))</f>
+        <f>AVEDEV(B6:B16)</f>
         <v/>
       </c>
       <c r="F16" s="15">
@@ -6890,7 +6878,7 @@
         <v/>
       </c>
       <c r="E17" s="15">
-        <f>MEDIAN(IF(B6:B17&gt;0,ABS(B6:B17-C17)))</f>
+        <f>AVEDEV(B6:B17)</f>
         <v/>
       </c>
       <c r="F17" s="15">
@@ -6924,7 +6912,7 @@
         <v/>
       </c>
       <c r="E18" s="15">
-        <f>MEDIAN(IF(B6:B18&gt;0,ABS(B6:B18-C18)))</f>
+        <f>AVEDEV(B6:B18)</f>
         <v/>
       </c>
       <c r="F18" s="15">
@@ -6958,7 +6946,7 @@
         <v/>
       </c>
       <c r="E19" s="15">
-        <f>MEDIAN(IF(B6:B19&gt;0,ABS(B6:B19-C19)))</f>
+        <f>AVEDEV(B6:B19)</f>
         <v/>
       </c>
       <c r="F19" s="15">
@@ -6992,7 +6980,7 @@
         <v/>
       </c>
       <c r="E20" s="15">
-        <f>MEDIAN(IF(B6:B20&gt;0,ABS(B6:B20-C20)))</f>
+        <f>AVEDEV(B6:B20)</f>
         <v/>
       </c>
       <c r="F20" s="15">
@@ -7026,7 +7014,7 @@
         <v/>
       </c>
       <c r="E21" s="15">
-        <f>MEDIAN(IF(B7:B21&gt;0,ABS(B7:B21-C21)))</f>
+        <f>AVEDEV(B7:B21)</f>
         <v/>
       </c>
       <c r="F21" s="15">
@@ -7060,7 +7048,7 @@
         <v/>
       </c>
       <c r="E22" s="15">
-        <f>MEDIAN(IF(B8:B22&gt;0,ABS(B8:B22-C22)))</f>
+        <f>AVEDEV(B8:B22)</f>
         <v/>
       </c>
       <c r="F22" s="15">
@@ -7094,7 +7082,7 @@
         <v/>
       </c>
       <c r="E23" s="15">
-        <f>MEDIAN(IF(B9:B23&gt;0,ABS(B9:B23-C23)))</f>
+        <f>AVEDEV(B9:B23)</f>
         <v/>
       </c>
       <c r="F23" s="15">
@@ -7128,7 +7116,7 @@
         <v/>
       </c>
       <c r="E24" s="15">
-        <f>MEDIAN(IF(B10:B24&gt;0,ABS(B10:B24-C24)))</f>
+        <f>AVEDEV(B10:B24)</f>
         <v/>
       </c>
       <c r="F24" s="15">
@@ -7162,7 +7150,7 @@
         <v/>
       </c>
       <c r="E25" s="15">
-        <f>MEDIAN(IF(B11:B25&gt;0,ABS(B11:B25-C25)))</f>
+        <f>AVEDEV(B11:B25)</f>
         <v/>
       </c>
       <c r="F25" s="15">
@@ -7196,7 +7184,7 @@
         <v/>
       </c>
       <c r="E26" s="15">
-        <f>MEDIAN(IF(B12:B26&gt;0,ABS(B12:B26-C26)))</f>
+        <f>AVEDEV(B12:B26)</f>
         <v/>
       </c>
       <c r="F26" s="15">
@@ -7230,7 +7218,7 @@
         <v/>
       </c>
       <c r="E27" s="15">
-        <f>MEDIAN(IF(B13:B27&gt;0,ABS(B13:B27-C27)))</f>
+        <f>AVEDEV(B13:B27)</f>
         <v/>
       </c>
       <c r="F27" s="15">
@@ -7264,7 +7252,7 @@
         <v/>
       </c>
       <c r="E28" s="15">
-        <f>MEDIAN(IF(B14:B28&gt;0,ABS(B14:B28-C28)))</f>
+        <f>AVEDEV(B14:B28)</f>
         <v/>
       </c>
       <c r="F28" s="15">
@@ -7298,7 +7286,7 @@
         <v/>
       </c>
       <c r="E29" s="15">
-        <f>MEDIAN(IF(B15:B29&gt;0,ABS(B15:B29-C29)))</f>
+        <f>AVEDEV(B15:B29)</f>
         <v/>
       </c>
       <c r="F29" s="15">
@@ -13728,7 +13716,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H22"/>
+  <autoFilter ref="A4:H21"/>
   <conditionalFormatting sqref="E5:E16">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"CRITICAL"</formula>
@@ -13752,7 +13740,7 @@
       <formula>"NO_DAYLIGHT"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E22">
+  <conditionalFormatting sqref="E5:E21">
     <cfRule type="cellIs" priority="8" operator="equal" dxfId="0">
       <formula>"CRITICAL"</formula>
     </cfRule>

--- a/docs/M2_PV_Performance_Workbook.xlsx
+++ b/docs/M2_PV_Performance_Workbook.xlsx
@@ -49,6 +49,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Helpers_SO" sheetId="40" state="visible" r:id="rId40"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SO_Economics" sheetId="41" state="visible" r:id="rId41"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SO_Summary" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Data_MR" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Helpers_MR" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M2b_MpptRatio" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M2b_MR_StringStatus" sheetId="46" state="visible" r:id="rId46"/>
   </sheets>
   <definedNames>
     <definedName name="cfg_critical_below">Config!$C$4</definedName>
@@ -137,6 +141,14 @@
     <definedName name="cfg_so_tariff">Config!$C$68</definedName>
     <definedName name="cfg_so_cleaning_cost">Config!$C$69</definedName>
     <definedName name="cfg_so_payback_thr">Config!$C$70</definedName>
+    <definedName name="cfg_mr_poa_threshold_wm2">Config!$C$71</definedName>
+    <definedName name="cfg_mr_poa_floor_wm2">Config!$C$72</definedName>
+    <definedName name="cfg_mr_ratio_threshold">Config!$C$73</definedName>
+    <definedName name="cfg_mr_ratio_high">Config!$C$74</definedName>
+    <definedName name="cfg_mr_ratio_critical">Config!$C$75</definedName>
+    <definedName name="cfg_mr_debounce_steps">Config!$C$76</definedName>
+    <definedName name="cfg_mr_min_partner">Config!$C$77</definedName>
+    <definedName name="cfg_mr_partner_clip">Config!$C$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Findings_Summary'!$A$4:$H$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -145,7 +157,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
@@ -154,6 +166,7 @@
     <numFmt numFmtId="169" formatCode="hh:mm"/>
     <numFmt numFmtId="170" formatCode="0.00000"/>
     <numFmt numFmtId="171" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="172" formatCode="0.0#"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -318,7 +331,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -400,6 +413,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -831,7 +846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -854,14 +869,14 @@
     <row r="2">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Peta tiap detektor → sinyal → fault_type → severity → status reproduksibilitas Excel. Workbook 41 detektor-sheet (di luar indeks ini). Detail: docs/M2_RE_0X_*.md + M2_Family_Summary.</t>
+          <t>Peta tiap detektor → sinyal → fault_type → severity → status reproduksibilitas Excel. Workbook 45 detektor-sheet (di luar indeks ini). Detail: docs/M2_RE_0X_*.md + M2_Family_Summary.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
         <is>
-          <t>1. Peta Detektor (8 aktif + 1 ML skeleton)</t>
+          <t>1. Peta Detektor (9 aktif + 1 ML skeleton)</t>
         </is>
       </c>
     </row>
@@ -1073,37 +1088,37 @@
       </c>
       <c r="B10" s="49" t="inlineStr">
         <is>
-          <t>M2IForest</t>
+          <t>M2bMpptRatio</t>
         </is>
       </c>
       <c r="C10" s="49" t="inlineStr">
         <is>
-          <t>iforest.py</t>
+          <t>mppt_ratio.py</t>
         </is>
       </c>
       <c r="D10" s="49" t="inlineStr">
         <is>
-          <t>IsolationForest 5-fitur (V,I,V_dev,I_dev,R)</t>
+          <t>I/median(partner se-MPPT) &lt; 0.85 + debounce 20</t>
         </is>
       </c>
       <c r="E10" s="49" t="inlineStr">
         <is>
-          <t>iforest_anomaly</t>
+          <t>mppt_partner_underperform</t>
         </is>
       </c>
       <c r="F10" s="49" t="inlineStr">
         <is>
-          <t>kuartil rank flagged: CRIT/HIGH/MED/INFO</t>
+          <t>rem&lt;0.20 CRIT · &lt;0.50 HIGH · else MED (conf 50–90)</t>
         </is>
       </c>
       <c r="G10" s="49" t="inlineStr">
         <is>
-          <t>IF_Anomaly</t>
-        </is>
-      </c>
-      <c r="H10" s="52" t="inlineStr">
-        <is>
-          <t>APPROKSIMASI</t>
+          <t>M2b_MpptRatio</t>
+        </is>
+      </c>
+      <c r="H10" s="50" t="inlineStr">
+        <is>
+          <t>PENUH</t>
         </is>
       </c>
     </row>
@@ -1113,37 +1128,37 @@
       </c>
       <c r="B11" s="49" t="inlineStr">
         <is>
-          <t>M2aLowIrradiance</t>
+          <t>M2IForest</t>
         </is>
       </c>
       <c r="C11" s="49" t="inlineStr">
         <is>
-          <t>m2a/low_irradiance.py</t>
+          <t>iforest.py</t>
         </is>
       </c>
       <c r="D11" s="49" t="inlineStr">
         <is>
-          <t>OLS slope PR_proxy vs POA (band low/mid)</t>
+          <t>IsolationForest 5-fitur (V,I,V_dev,I_dev,R)</t>
         </is>
       </c>
       <c r="E11" s="49" t="inlineStr">
         <is>
-          <t>low_irradiance / general_underperform</t>
+          <t>iforest_anomaly</t>
         </is>
       </c>
       <c r="F11" s="49" t="inlineStr">
         <is>
-          <t>|slope_low|·r² → CRIT/HIGH/MED</t>
+          <t>kuartil rank flagged: CRIT/HIGH/MED/INFO</t>
         </is>
       </c>
       <c r="G11" s="49" t="inlineStr">
         <is>
-          <t>M2a_LowIrradiance</t>
-        </is>
-      </c>
-      <c r="H11" s="50" t="inlineStr">
-        <is>
-          <t>PENUH</t>
+          <t>IF_Anomaly</t>
+        </is>
+      </c>
+      <c r="H11" s="52" t="inlineStr">
+        <is>
+          <t>APPROKSIMASI</t>
         </is>
       </c>
     </row>
@@ -1153,32 +1168,32 @@
       </c>
       <c r="B12" s="49" t="inlineStr">
         <is>
-          <t>M2aShading</t>
+          <t>M2aLowIrradiance</t>
         </is>
       </c>
       <c r="C12" s="49" t="inlineStr">
         <is>
-          <t>m2a/shading.py</t>
+          <t>m2a/low_irradiance.py</t>
         </is>
       </c>
       <c r="D12" s="49" t="inlineStr">
         <is>
-          <t>CV antar-string per jam + PR + asimetri AM/PM</t>
+          <t>OLS slope PR_proxy vs POA (band low/mid)</t>
         </is>
       </c>
       <c r="E12" s="49" t="inlineStr">
         <is>
-          <t>shading_morning/afternoon/uniform</t>
+          <t>low_irradiance / general_underperform</t>
         </is>
       </c>
       <c r="F12" s="49" t="inlineStr">
         <is>
-          <t>0.7·frac + 0.3·asym → CRIT/HIGH/MED</t>
+          <t>|slope_low|·r² → CRIT/HIGH/MED</t>
         </is>
       </c>
       <c r="G12" s="49" t="inlineStr">
         <is>
-          <t>M2a_Shading</t>
+          <t>M2a_LowIrradiance</t>
         </is>
       </c>
       <c r="H12" s="50" t="inlineStr">
@@ -1193,37 +1208,37 @@
       </c>
       <c r="B13" s="49" t="inlineStr">
         <is>
-          <t>M2aSoiling</t>
+          <t>M2aShading</t>
         </is>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
-          <t>m2a/soiling.py (skeleton)</t>
+          <t>m2a/shading.py</t>
         </is>
       </c>
       <c r="D13" s="49" t="inlineStr">
         <is>
-          <t>rdtools SRR (Monte-Carlo) → ekonomi payback</t>
+          <t>CV antar-string per jam + PR + asimetri AM/PM</t>
         </is>
       </c>
       <c r="E13" s="49" t="inlineStr">
         <is>
-          <t>soiling_detected / cleaning_recommended / insufficient_data</t>
+          <t>shading_morning/afternoon/uniform</t>
         </is>
       </c>
       <c r="F13" s="49" t="inlineStr">
         <is>
-          <t>(p_loss,payback) → CRIT/HIGH/MED/INFO</t>
+          <t>0.7·frac + 0.3·asym → CRIT/HIGH/MED</t>
         </is>
       </c>
       <c r="G13" s="49" t="inlineStr">
         <is>
-          <t>SO_Economics</t>
-        </is>
-      </c>
-      <c r="H13" s="53" t="inlineStr">
-        <is>
-          <t>HILIR PENUH</t>
+          <t>M2a_Shading</t>
+        </is>
+      </c>
+      <c r="H13" s="50" t="inlineStr">
+        <is>
+          <t>PENUH</t>
         </is>
       </c>
     </row>
@@ -1233,353 +1248,415 @@
       </c>
       <c r="B14" s="49" t="inlineStr">
         <is>
+          <t>M2aSoiling</t>
+        </is>
+      </c>
+      <c r="C14" s="49" t="inlineStr">
+        <is>
+          <t>m2a/soiling.py (skeleton)</t>
+        </is>
+      </c>
+      <c r="D14" s="49" t="inlineStr">
+        <is>
+          <t>rdtools SRR (Monte-Carlo) → ekonomi payback</t>
+        </is>
+      </c>
+      <c r="E14" s="49" t="inlineStr">
+        <is>
+          <t>soiling_detected / cleaning_recommended / insufficient_data</t>
+        </is>
+      </c>
+      <c r="F14" s="49" t="inlineStr">
+        <is>
+          <t>(p_loss,payback) → CRIT/HIGH/MED/INFO</t>
+        </is>
+      </c>
+      <c r="G14" s="49" t="inlineStr">
+        <is>
+          <t>SO_Economics</t>
+        </is>
+      </c>
+      <c r="H14" s="53" t="inlineStr">
+        <is>
+          <t>HILIR PENUH</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="49" t="inlineStr">
+        <is>
           <t>M2bIntermittent (LSTM-AE)</t>
         </is>
       </c>
-      <c r="C14" s="49" t="inlineStr">
+      <c r="C15" s="49" t="inlineStr">
         <is>
           <t>lstm_ae.py (skeleton, enabled=False)</t>
         </is>
       </c>
-      <c r="D14" s="49" t="inlineStr">
+      <c r="D15" s="49" t="inlineStr">
         <is>
           <t>LSTM Autoencoder; reconstruction error window 24-jam (96×15-min)</t>
         </is>
       </c>
-      <c r="E14" s="49" t="inlineStr">
+      <c r="E15" s="49" t="inlineStr">
         <is>
           <t>intermittent</t>
         </is>
       </c>
-      <c r="F14" s="49" t="inlineStr">
+      <c r="F15" s="49" t="inlineStr">
         <is>
           <t>MEDIUM (conf 70)</t>
         </is>
       </c>
-      <c r="G14" s="49" t="inlineStr">
+      <c r="G15" s="49" t="inlineStr">
         <is>
           <t>(tak ada — input-only)</t>
         </is>
       </c>
-      <c r="H14" s="59" t="inlineStr">
+      <c r="H15" s="59" t="inlineStr">
         <is>
           <t>INPUT-ONLY</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="48" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="48" t="inlineStr">
         <is>
           <t>Legenda Status Excel</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="54" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="54" t="inlineStr">
         <is>
           <t>PENUH</t>
         </is>
       </c>
-      <c r="B17" s="49" t="inlineStr">
+      <c r="B18" s="49" t="inlineStr">
         <is>
           <t>Direproduksi eksak sebagai formula live (verified vs source, selisih ~0).</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="55" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="55" t="inlineStr">
         <is>
           <t>PENUH*</t>
         </is>
       </c>
-      <c r="B18" s="49" t="inlineStr">
+      <c r="B19" s="49" t="inlineStr">
         <is>
           <t>Per-inverter math live &amp; eksak; SATU input representatif: fleet V_gnd median/std (ground_fault).</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="56" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="56" t="inlineStr">
         <is>
           <t>HILIR PENUH</t>
         </is>
       </c>
-      <c r="B19" s="49" t="inlineStr">
+      <c r="B20" s="49" t="inlineStr">
         <is>
           <t>Semua hilir live &amp; eksak; satu nilai = INPUT black-box: soiling_ratio dari SRR Monte-Carlo.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="57" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="57" t="inlineStr">
         <is>
           <t>APPROKSIMASI</t>
         </is>
       </c>
-      <c r="B20" s="49" t="inlineStr">
+      <c r="B21" s="49" t="inlineStr">
         <is>
           <t>Struktur faithful tapi SKOR proxy (MAD), BUKAN skor IsolationForest asli — menandai sampel berbeda.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="60" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="60" t="inlineStr">
         <is>
           <t>INPUT-ONLY</t>
         </is>
       </c>
-      <c r="B21" s="49" t="inlineStr">
+      <c r="B22" s="49" t="inlineStr">
         <is>
           <t>Jaringan PyTorch terlatih = black box; TAK ADA sheet &amp; tak ada lapisan hilir bermakna (LSTM-AE). Lihat M2_RE_10.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="48" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="48" t="inlineStr">
         <is>
           <t>2. Inventaris Sheet &amp; Dokumen (per iterasi)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Iterasi</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Detector</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Dokumen RE</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>Sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B25" s="49" t="inlineStr">
-        <is>
-          <t>Inti (shared)</t>
-        </is>
-      </c>
-      <c r="C25" s="49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D25" s="49" t="inlineStr">
-        <is>
-          <t>README, Config</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="B26" s="49" t="inlineStr">
         <is>
-          <t>M2eAvailability</t>
+          <t>Inti (shared)</t>
         </is>
       </c>
       <c r="C26" s="49" t="inlineStr">
         <is>
-          <t>(Iterasi 2)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D26" s="49" t="inlineStr">
         <is>
-          <t>Raw_Data, EmptyPVMap, Helpers_M2e, M2e_Availability, M2e_AllStrings, Findings_Summary</t>
+          <t>README, Config</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B27" s="49" t="inlineStr">
         <is>
-          <t>M2bPeerZScore</t>
+          <t>M2eAvailability</t>
         </is>
       </c>
       <c r="C27" s="49" t="inlineStr">
         <is>
-          <t>M2_RE_03</t>
+          <t>(Iterasi 2)</t>
         </is>
       </c>
       <c r="D27" s="49" t="inlineStr">
         <is>
-          <t>PanelSpec, Raw_Data_M2b, Meteo_Dummy, Helpers_M2b, M2b_PeerZScore, M2b_StringStatus, M2b_StatComparison, Hampel_Preprocessing</t>
+          <t>Raw_Data, EmptyPVMap, Helpers_M2e, M2e_Availability, M2e_AllStrings, Findings_Summary</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B28" s="49" t="inlineStr">
         <is>
-          <t>M2bOpenCircuit</t>
+          <t>M2bPeerZScore</t>
         </is>
       </c>
       <c r="C28" s="49" t="inlineStr">
         <is>
-          <t>M2_RE_04</t>
+          <t>M2_RE_03</t>
         </is>
       </c>
       <c r="D28" s="49" t="inlineStr">
         <is>
-          <t>Raw_Data_OC, Helpers_OC, M2b_OpenCircuit, M2b_OC_StringStatus</t>
+          <t>PanelSpec, Raw_Data_M2b, Meteo_Dummy, Helpers_M2b, M2b_PeerZScore, M2b_StringStatus, M2b_StatComparison, Hampel_Preprocessing</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B29" s="49" t="inlineStr">
         <is>
-          <t>M2bGroundFault</t>
+          <t>M2bOpenCircuit</t>
         </is>
       </c>
       <c r="C29" s="49" t="inlineStr">
         <is>
-          <t>M2_RE_05</t>
+          <t>M2_RE_04</t>
         </is>
       </c>
       <c r="D29" s="49" t="inlineStr">
         <is>
-          <t>Raw_Data_GF, Helpers_GF, GF_StringMetrics, M2c_GroundFault, M2c_GF_StringStatus</t>
+          <t>Raw_Data_OC, Helpers_OC, M2b_OpenCircuit, M2b_OC_StringStatus</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B30" s="49" t="inlineStr">
         <is>
-          <t>M2IForest</t>
+          <t>M2bGroundFault</t>
         </is>
       </c>
       <c r="C30" s="49" t="inlineStr">
         <is>
-          <t>M2_RE_06</t>
+          <t>M2_RE_05</t>
         </is>
       </c>
       <c r="D30" s="49" t="inlineStr">
         <is>
-          <t>Raw_Data_IF, Features_IF, IF_Anomaly, IF_Summary</t>
+          <t>Raw_Data_GF, Helpers_GF, GF_StringMetrics, M2c_GroundFault, M2c_GF_StringStatus</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B31" s="49" t="inlineStr">
         <is>
-          <t>M2aLowIrradiance</t>
+          <t>M2IForest</t>
         </is>
       </c>
       <c r="C31" s="49" t="inlineStr">
         <is>
-          <t>M2_RE_07</t>
+          <t>M2_RE_06</t>
         </is>
       </c>
       <c r="D31" s="49" t="inlineStr">
         <is>
-          <t>Raw_Data_LI, Helpers_LI, M2a_LowIrradiance, LI_Summary</t>
+          <t>Raw_Data_IF, Features_IF, IF_Anomaly, IF_Summary</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B32" s="49" t="inlineStr">
         <is>
-          <t>M2aShading</t>
+          <t>M2aLowIrradiance</t>
         </is>
       </c>
       <c r="C32" s="49" t="inlineStr">
         <is>
-          <t>M2_RE_08</t>
+          <t>M2_RE_07</t>
         </is>
       </c>
       <c r="D32" s="49" t="inlineStr">
         <is>
-          <t>Raw_Data_SH, Helpers_SH, SH_Hourly, M2a_Shading</t>
+          <t>Raw_Data_LI, Helpers_LI, M2a_LowIrradiance, LI_Summary</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B33" s="49" t="inlineStr">
         <is>
-          <t>M2aSoiling</t>
+          <t>M2aShading</t>
         </is>
       </c>
       <c r="C33" s="49" t="inlineStr">
         <is>
-          <t>M2_RE_09</t>
+          <t>M2_RE_08</t>
         </is>
       </c>
       <c r="D33" s="49" t="inlineStr">
         <is>
-          <t>Raw_Data_SO, Helpers_SO, SO_Economics, SO_Summary</t>
+          <t>Raw_Data_SH, Helpers_SH, SH_Hourly, M2a_Shading</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="49" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B34" s="49" t="inlineStr">
+        <is>
+          <t>M2aSoiling</t>
+        </is>
+      </c>
+      <c r="C34" s="49" t="inlineStr">
+        <is>
+          <t>M2_RE_09</t>
+        </is>
+      </c>
+      <c r="D34" s="49" t="inlineStr">
+        <is>
+          <t>Raw_Data_SO, Helpers_SO, SO_Economics, SO_Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="49" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B34" s="49" t="inlineStr">
+      <c r="B35" s="49" t="inlineStr">
         <is>
           <t>M2bIntermittent (LSTM-AE)</t>
         </is>
       </c>
-      <c r="C34" s="49" t="inlineStr">
+      <c r="C35" s="49" t="inlineStr">
         <is>
           <t>M2_RE_10</t>
         </is>
       </c>
-      <c r="D34" s="49" t="inlineStr">
+      <c r="D35" s="49" t="inlineStr">
         <is>
           <t>(tak ada sheet — input-only; jaringan PyTorch terlatih)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B36" s="49" t="inlineStr">
+        <is>
+          <t>M2bMpptRatio</t>
+        </is>
+      </c>
+      <c r="C36" s="49" t="inlineStr">
+        <is>
+          <t>M2_RE_11</t>
+        </is>
+      </c>
+      <c r="D36" s="49" t="inlineStr">
+        <is>
+          <t>Raw_Data_MR, Helpers_MR, M2b_MpptRatio, M2b_MR_StringStatus</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -11641,49 +11718,71 @@
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>M2bMpptRatio</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Raw_Data_MR, Helpers_MR, M2b_MpptRatio, M2b_MR_StringStatus</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>Cara membaca</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
-        <is>
-          <t>• Sheet 'Config' adalah single source of truth untuk semua threshold. Edit di sini → seluruh workbook recalc.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>• Sheet 'Raw_Data' berisi data dummy realistis. Ganti dengan data aktual mu (paste over) untuk pakai workbook ini di lapangan.</t>
+          <t>• Sheet 'Config' adalah single source of truth untuk semua threshold. Edit di sini → seluruh workbook recalc.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>• Sheet 'Helpers_M2e' adalah JEMBATAN antara Raw_Data dan M2e_Availability. Tiap kolom punya formula yang ekuivalen dengan satu langkah di pv_pipeline/availability.py.</t>
+          <t>• Sheet 'Raw_Data' berisi data dummy realistis. Ganti dengan data aktual mu (paste over) untuk pakai workbook ini di lapangan.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>• Sheet 'M2e_Availability' menampilkan hasil akhir per inverter &amp; per string + severity. Sheet 'M2e_AllStrings' mereplika output sheet xlsx Python.</t>
+          <t>• Sheet 'Helpers_M2e' adalah JEMBATAN antara Raw_Data dan M2e_Availability. Tiap kolom punya formula yang ekuivalen dengan satu langkah di pv_pipeline/availability.py.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="30" t="inlineStr">
         <is>
-          <t>• Severity dihitung via IFS() dari uptime_pct ke threshold di Config.</t>
+          <t>• Sheet 'M2e_Availability' menampilkan hasil akhir per inverter &amp; per string + severity. Sheet 'M2e_AllStrings' mereplika output sheet xlsx Python.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>• Severity dihitung via IFS() dari uptime_pct ke threshold di Config.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>• Workbook ini akan TUMBUH per iterasi — sheet baru ditambah tanpa mengubah yang lama.</t>
         </is>
@@ -30738,7 +30837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -32117,6 +32216,166 @@
       <c r="D70" s="5" t="inlineStr">
         <is>
           <t>payback &lt; ini → recommend cleaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>m2b_mppt_ratio</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>poa_threshold_wm2</t>
+        </is>
+      </c>
+      <c r="C71" s="22" t="n">
+        <v>300</v>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>moderate sun gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>m2b_mppt_ratio</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>poa_floor_wm2</t>
+        </is>
+      </c>
+      <c r="C72" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>hard floor twilight</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>m2b_mppt_ratio</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>ratio_threshold</t>
+        </is>
+      </c>
+      <c r="C73" s="22" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>I&lt;85% median partner -&gt; qualifying</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>m2b_mppt_ratio</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>ratio_high</t>
+        </is>
+      </c>
+      <c r="C74" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>event_median&lt;0.50 -&gt; HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>m2b_mppt_ratio</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>ratio_critical</t>
+        </is>
+      </c>
+      <c r="C75" s="22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>event_median&lt;0.20 -&gt; CRITICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>m2b_mppt_ratio</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>debounce_consecutive_steps</t>
+        </is>
+      </c>
+      <c r="C76" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>~100 menit @ 5-min</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>m2b_mppt_ratio</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>min_partner_strings</t>
+        </is>
+      </c>
+      <c r="C77" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>grup 2-string tetap dianalisis</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>m2b_mppt_ratio</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>partner_clip</t>
+        </is>
+      </c>
+      <c r="C78" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>clip(lower=0.01) divide-by-zero guard</t>
         </is>
       </c>
     </row>
@@ -43946,6 +44205,6486 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Raw_Data_MR — arus per-string 1 inverter (2 MPPT group) + POA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Model SUN2000-330KTL-H1 (WB03-10): MPPT1=[PV1-4], MPPT2=[PV5-9] — persis config/strings.yaml.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>Arus konstan per string (sun di-faktorkan keluar; ratio invarian POA). PV9 glitch 3 langkah (baris 9-11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>POA (W/m^2)</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>PV1 input current(A)</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>PV2 input current(A)</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>PV3 input current(A)</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>PV4 input current(A)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>PV5 input current(A)</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>PV6 input current(A)</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>PV7 input current(A)</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>PV8 input current(A)</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>PV9 input current(A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="40" t="n">
+        <v>46156.5</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="40" t="n">
+        <v>46156.50347222222</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="40" t="n">
+        <v>46156.50694444445</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="40" t="n">
+        <v>46156.51041666666</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="40" t="n">
+        <v>46156.51388888889</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="40" t="n">
+        <v>46156.51736111111</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="n">
+        <v>46156.52083333334</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="40" t="n">
+        <v>46156.52430555555</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="40" t="n">
+        <v>46156.52777777778</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="n">
+        <v>46156.53125</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="n">
+        <v>46156.53472222222</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="n">
+        <v>46156.53819444445</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="n">
+        <v>46156.54166666666</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="40" t="n">
+        <v>46156.54513888889</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="40" t="n">
+        <v>46156.54861111111</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="40" t="n">
+        <v>46156.55208333334</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="40" t="n">
+        <v>46156.55555555555</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D21" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="40" t="n">
+        <v>46156.55902777778</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="40" t="n">
+        <v>46156.5625</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="40" t="n">
+        <v>46156.56597222222</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="40" t="n">
+        <v>46156.56944444445</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="40" t="n">
+        <v>46156.57291666666</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="40" t="n">
+        <v>46156.57638888889</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C27" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="40" t="n">
+        <v>46156.57986111111</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="40" t="n">
+        <v>46156.75694444445</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="C29" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="40" t="n">
+        <v>46156.76388888889</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="C30" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="15" t="n">
+        <v>12.85</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AM30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Helpers_MR — daylight + median partner se-MPPT + ratio + qualifying + running-consec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>daylight = (POA&gt;cfg_mr_poa_threshold) &amp; (POA&gt;cfg_mr_poa_floor)  [sub-gate POA saja; ephemeris di luar sheet].</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>median partner = MEDIAN(cell partner se-MPPT)  -&gt; meniru median(axis=1) atas sibling (mppt_ratio.py baris 274-276).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>POA</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>daylight</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>med_partner_PV1</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>med_partner_PV2</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>med_partner_PV3</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>med_partner_PV4</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>med_partner_PV5</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>med_partner_PV6</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>med_partner_PV7</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>med_partner_PV8</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>med_partner_PV9</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>ratio_PV1</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>ratio_PV2</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>ratio_PV3</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>ratio_PV4</t>
+        </is>
+      </c>
+      <c r="Q4" s="10" t="inlineStr">
+        <is>
+          <t>ratio_PV5</t>
+        </is>
+      </c>
+      <c r="R4" s="10" t="inlineStr">
+        <is>
+          <t>ratio_PV6</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>ratio_PV7</t>
+        </is>
+      </c>
+      <c r="T4" s="10" t="inlineStr">
+        <is>
+          <t>ratio_PV8</t>
+        </is>
+      </c>
+      <c r="U4" s="10" t="inlineStr">
+        <is>
+          <t>ratio_PV9</t>
+        </is>
+      </c>
+      <c r="V4" s="10" t="inlineStr">
+        <is>
+          <t>qual_PV1</t>
+        </is>
+      </c>
+      <c r="W4" s="10" t="inlineStr">
+        <is>
+          <t>qual_PV2</t>
+        </is>
+      </c>
+      <c r="X4" s="10" t="inlineStr">
+        <is>
+          <t>qual_PV3</t>
+        </is>
+      </c>
+      <c r="Y4" s="10" t="inlineStr">
+        <is>
+          <t>qual_PV4</t>
+        </is>
+      </c>
+      <c r="Z4" s="10" t="inlineStr">
+        <is>
+          <t>qual_PV5</t>
+        </is>
+      </c>
+      <c r="AA4" s="10" t="inlineStr">
+        <is>
+          <t>qual_PV6</t>
+        </is>
+      </c>
+      <c r="AB4" s="10" t="inlineStr">
+        <is>
+          <t>qual_PV7</t>
+        </is>
+      </c>
+      <c r="AC4" s="10" t="inlineStr">
+        <is>
+          <t>qual_PV8</t>
+        </is>
+      </c>
+      <c r="AD4" s="10" t="inlineStr">
+        <is>
+          <t>qual_PV9</t>
+        </is>
+      </c>
+      <c r="AE4" s="10" t="inlineStr">
+        <is>
+          <t>consec_PV1</t>
+        </is>
+      </c>
+      <c r="AF4" s="10" t="inlineStr">
+        <is>
+          <t>consec_PV2</t>
+        </is>
+      </c>
+      <c r="AG4" s="10" t="inlineStr">
+        <is>
+          <t>consec_PV3</t>
+        </is>
+      </c>
+      <c r="AH4" s="10" t="inlineStr">
+        <is>
+          <t>consec_PV4</t>
+        </is>
+      </c>
+      <c r="AI4" s="10" t="inlineStr">
+        <is>
+          <t>consec_PV5</t>
+        </is>
+      </c>
+      <c r="AJ4" s="10" t="inlineStr">
+        <is>
+          <t>consec_PV6</t>
+        </is>
+      </c>
+      <c r="AK4" s="10" t="inlineStr">
+        <is>
+          <t>consec_PV7</t>
+        </is>
+      </c>
+      <c r="AL4" s="10" t="inlineStr">
+        <is>
+          <t>consec_PV8</t>
+        </is>
+      </c>
+      <c r="AM4" s="10" t="inlineStr">
+        <is>
+          <t>consec_PV9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="40">
+        <f>Raw_Data_MR!A5</f>
+        <v/>
+      </c>
+      <c r="B5" s="5">
+        <f>Raw_Data_MR!B5</f>
+        <v/>
+      </c>
+      <c r="C5" s="5">
+        <f>IF(AND(B5&gt;cfg_mr_poa_threshold_wm2,B5&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D5" s="17">
+        <f>MEDIAN(Raw_Data_MR!D5,Raw_Data_MR!E5,Raw_Data_MR!F5)</f>
+        <v/>
+      </c>
+      <c r="E5" s="17">
+        <f>MEDIAN(Raw_Data_MR!C5,Raw_Data_MR!E5,Raw_Data_MR!F5)</f>
+        <v/>
+      </c>
+      <c r="F5" s="17">
+        <f>MEDIAN(Raw_Data_MR!C5,Raw_Data_MR!D5,Raw_Data_MR!F5)</f>
+        <v/>
+      </c>
+      <c r="G5" s="17">
+        <f>MEDIAN(Raw_Data_MR!C5,Raw_Data_MR!D5,Raw_Data_MR!E5)</f>
+        <v/>
+      </c>
+      <c r="H5" s="17">
+        <f>MEDIAN(Raw_Data_MR!H5,Raw_Data_MR!I5,Raw_Data_MR!J5,Raw_Data_MR!K5)</f>
+        <v/>
+      </c>
+      <c r="I5" s="17">
+        <f>MEDIAN(Raw_Data_MR!G5,Raw_Data_MR!I5,Raw_Data_MR!J5,Raw_Data_MR!K5)</f>
+        <v/>
+      </c>
+      <c r="J5" s="17">
+        <f>MEDIAN(Raw_Data_MR!G5,Raw_Data_MR!H5,Raw_Data_MR!J5,Raw_Data_MR!K5)</f>
+        <v/>
+      </c>
+      <c r="K5" s="17">
+        <f>MEDIAN(Raw_Data_MR!G5,Raw_Data_MR!H5,Raw_Data_MR!I5,Raw_Data_MR!K5)</f>
+        <v/>
+      </c>
+      <c r="L5" s="17">
+        <f>MEDIAN(Raw_Data_MR!G5,Raw_Data_MR!H5,Raw_Data_MR!I5,Raw_Data_MR!J5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="31">
+        <f>Raw_Data_MR!C5/MAX(D5,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N5" s="31">
+        <f>Raw_Data_MR!D5/MAX(E5,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O5" s="31">
+        <f>Raw_Data_MR!E5/MAX(F5,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P5" s="31">
+        <f>Raw_Data_MR!F5/MAX(G5,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q5" s="31">
+        <f>Raw_Data_MR!G5/MAX(H5,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R5" s="31">
+        <f>Raw_Data_MR!H5/MAX(I5,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S5" s="31">
+        <f>Raw_Data_MR!I5/MAX(J5,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T5" s="31">
+        <f>Raw_Data_MR!J5/MAX(K5,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U5" s="31">
+        <f>Raw_Data_MR!K5/MAX(L5,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V5" s="5">
+        <f>IF(AND(M5&lt;cfg_mr_ratio_threshold,$C5=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W5" s="5">
+        <f>IF(AND(N5&lt;cfg_mr_ratio_threshold,$C5=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X5" s="5">
+        <f>IF(AND(O5&lt;cfg_mr_ratio_threshold,$C5=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y5" s="5">
+        <f>IF(AND(P5&lt;cfg_mr_ratio_threshold,$C5=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z5" s="5">
+        <f>IF(AND(Q5&lt;cfg_mr_ratio_threshold,$C5=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA5" s="5">
+        <f>IF(AND(R5&lt;cfg_mr_ratio_threshold,$C5=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB5" s="5">
+        <f>IF(AND(S5&lt;cfg_mr_ratio_threshold,$C5=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC5" s="5">
+        <f>IF(AND(T5&lt;cfg_mr_ratio_threshold,$C5=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD5" s="5">
+        <f>IF(AND(U5&lt;cfg_mr_ratio_threshold,$C5=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE5" s="5">
+        <f>V5</f>
+        <v/>
+      </c>
+      <c r="AF5" s="5">
+        <f>W5</f>
+        <v/>
+      </c>
+      <c r="AG5" s="5">
+        <f>X5</f>
+        <v/>
+      </c>
+      <c r="AH5" s="5">
+        <f>Y5</f>
+        <v/>
+      </c>
+      <c r="AI5" s="5">
+        <f>Z5</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="5">
+        <f>AA5</f>
+        <v/>
+      </c>
+      <c r="AK5" s="5">
+        <f>AB5</f>
+        <v/>
+      </c>
+      <c r="AL5" s="5">
+        <f>AC5</f>
+        <v/>
+      </c>
+      <c r="AM5" s="5">
+        <f>AD5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="40">
+        <f>Raw_Data_MR!A6</f>
+        <v/>
+      </c>
+      <c r="B6" s="5">
+        <f>Raw_Data_MR!B6</f>
+        <v/>
+      </c>
+      <c r="C6" s="5">
+        <f>IF(AND(B6&gt;cfg_mr_poa_threshold_wm2,B6&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="17">
+        <f>MEDIAN(Raw_Data_MR!D6,Raw_Data_MR!E6,Raw_Data_MR!F6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="17">
+        <f>MEDIAN(Raw_Data_MR!C6,Raw_Data_MR!E6,Raw_Data_MR!F6)</f>
+        <v/>
+      </c>
+      <c r="F6" s="17">
+        <f>MEDIAN(Raw_Data_MR!C6,Raw_Data_MR!D6,Raw_Data_MR!F6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="17">
+        <f>MEDIAN(Raw_Data_MR!C6,Raw_Data_MR!D6,Raw_Data_MR!E6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="17">
+        <f>MEDIAN(Raw_Data_MR!H6,Raw_Data_MR!I6,Raw_Data_MR!J6,Raw_Data_MR!K6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="17">
+        <f>MEDIAN(Raw_Data_MR!G6,Raw_Data_MR!I6,Raw_Data_MR!J6,Raw_Data_MR!K6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="17">
+        <f>MEDIAN(Raw_Data_MR!G6,Raw_Data_MR!H6,Raw_Data_MR!J6,Raw_Data_MR!K6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="17">
+        <f>MEDIAN(Raw_Data_MR!G6,Raw_Data_MR!H6,Raw_Data_MR!I6,Raw_Data_MR!K6)</f>
+        <v/>
+      </c>
+      <c r="L6" s="17">
+        <f>MEDIAN(Raw_Data_MR!G6,Raw_Data_MR!H6,Raw_Data_MR!I6,Raw_Data_MR!J6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="31">
+        <f>Raw_Data_MR!C6/MAX(D6,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N6" s="31">
+        <f>Raw_Data_MR!D6/MAX(E6,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O6" s="31">
+        <f>Raw_Data_MR!E6/MAX(F6,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P6" s="31">
+        <f>Raw_Data_MR!F6/MAX(G6,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q6" s="31">
+        <f>Raw_Data_MR!G6/MAX(H6,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R6" s="31">
+        <f>Raw_Data_MR!H6/MAX(I6,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S6" s="31">
+        <f>Raw_Data_MR!I6/MAX(J6,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T6" s="31">
+        <f>Raw_Data_MR!J6/MAX(K6,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U6" s="31">
+        <f>Raw_Data_MR!K6/MAX(L6,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V6" s="5">
+        <f>IF(AND(M6&lt;cfg_mr_ratio_threshold,$C6=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W6" s="5">
+        <f>IF(AND(N6&lt;cfg_mr_ratio_threshold,$C6=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X6" s="5">
+        <f>IF(AND(O6&lt;cfg_mr_ratio_threshold,$C6=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y6" s="5">
+        <f>IF(AND(P6&lt;cfg_mr_ratio_threshold,$C6=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z6" s="5">
+        <f>IF(AND(Q6&lt;cfg_mr_ratio_threshold,$C6=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA6" s="5">
+        <f>IF(AND(R6&lt;cfg_mr_ratio_threshold,$C6=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB6" s="5">
+        <f>IF(AND(S6&lt;cfg_mr_ratio_threshold,$C6=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC6" s="5">
+        <f>IF(AND(T6&lt;cfg_mr_ratio_threshold,$C6=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD6" s="5">
+        <f>IF(AND(U6&lt;cfg_mr_ratio_threshold,$C6=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE6" s="5">
+        <f>IF(V6=1,AE5+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF6" s="5">
+        <f>IF(W6=1,AF5+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG6" s="5">
+        <f>IF(X6=1,AG5+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH6" s="5">
+        <f>IF(Y6=1,AH5+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI6" s="5">
+        <f>IF(Z6=1,AI5+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="5">
+        <f>IF(AA6=1,AJ5+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK6" s="5">
+        <f>IF(AB6=1,AK5+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL6" s="5">
+        <f>IF(AC6=1,AL5+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM6" s="5">
+        <f>IF(AD6=1,AM5+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="40">
+        <f>Raw_Data_MR!A7</f>
+        <v/>
+      </c>
+      <c r="B7" s="5">
+        <f>Raw_Data_MR!B7</f>
+        <v/>
+      </c>
+      <c r="C7" s="5">
+        <f>IF(AND(B7&gt;cfg_mr_poa_threshold_wm2,B7&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="17">
+        <f>MEDIAN(Raw_Data_MR!D7,Raw_Data_MR!E7,Raw_Data_MR!F7)</f>
+        <v/>
+      </c>
+      <c r="E7" s="17">
+        <f>MEDIAN(Raw_Data_MR!C7,Raw_Data_MR!E7,Raw_Data_MR!F7)</f>
+        <v/>
+      </c>
+      <c r="F7" s="17">
+        <f>MEDIAN(Raw_Data_MR!C7,Raw_Data_MR!D7,Raw_Data_MR!F7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="17">
+        <f>MEDIAN(Raw_Data_MR!C7,Raw_Data_MR!D7,Raw_Data_MR!E7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="17">
+        <f>MEDIAN(Raw_Data_MR!H7,Raw_Data_MR!I7,Raw_Data_MR!J7,Raw_Data_MR!K7)</f>
+        <v/>
+      </c>
+      <c r="I7" s="17">
+        <f>MEDIAN(Raw_Data_MR!G7,Raw_Data_MR!I7,Raw_Data_MR!J7,Raw_Data_MR!K7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="17">
+        <f>MEDIAN(Raw_Data_MR!G7,Raw_Data_MR!H7,Raw_Data_MR!J7,Raw_Data_MR!K7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="17">
+        <f>MEDIAN(Raw_Data_MR!G7,Raw_Data_MR!H7,Raw_Data_MR!I7,Raw_Data_MR!K7)</f>
+        <v/>
+      </c>
+      <c r="L7" s="17">
+        <f>MEDIAN(Raw_Data_MR!G7,Raw_Data_MR!H7,Raw_Data_MR!I7,Raw_Data_MR!J7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="31">
+        <f>Raw_Data_MR!C7/MAX(D7,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N7" s="31">
+        <f>Raw_Data_MR!D7/MAX(E7,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O7" s="31">
+        <f>Raw_Data_MR!E7/MAX(F7,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P7" s="31">
+        <f>Raw_Data_MR!F7/MAX(G7,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q7" s="31">
+        <f>Raw_Data_MR!G7/MAX(H7,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R7" s="31">
+        <f>Raw_Data_MR!H7/MAX(I7,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S7" s="31">
+        <f>Raw_Data_MR!I7/MAX(J7,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T7" s="31">
+        <f>Raw_Data_MR!J7/MAX(K7,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U7" s="31">
+        <f>Raw_Data_MR!K7/MAX(L7,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V7" s="5">
+        <f>IF(AND(M7&lt;cfg_mr_ratio_threshold,$C7=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W7" s="5">
+        <f>IF(AND(N7&lt;cfg_mr_ratio_threshold,$C7=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X7" s="5">
+        <f>IF(AND(O7&lt;cfg_mr_ratio_threshold,$C7=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y7" s="5">
+        <f>IF(AND(P7&lt;cfg_mr_ratio_threshold,$C7=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z7" s="5">
+        <f>IF(AND(Q7&lt;cfg_mr_ratio_threshold,$C7=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA7" s="5">
+        <f>IF(AND(R7&lt;cfg_mr_ratio_threshold,$C7=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB7" s="5">
+        <f>IF(AND(S7&lt;cfg_mr_ratio_threshold,$C7=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC7" s="5">
+        <f>IF(AND(T7&lt;cfg_mr_ratio_threshold,$C7=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD7" s="5">
+        <f>IF(AND(U7&lt;cfg_mr_ratio_threshold,$C7=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE7" s="5">
+        <f>IF(V7=1,AE6+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF7" s="5">
+        <f>IF(W7=1,AF6+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG7" s="5">
+        <f>IF(X7=1,AG6+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH7" s="5">
+        <f>IF(Y7=1,AH6+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI7" s="5">
+        <f>IF(Z7=1,AI6+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="5">
+        <f>IF(AA7=1,AJ6+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK7" s="5">
+        <f>IF(AB7=1,AK6+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL7" s="5">
+        <f>IF(AC7=1,AL6+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM7" s="5">
+        <f>IF(AD7=1,AM6+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="40">
+        <f>Raw_Data_MR!A8</f>
+        <v/>
+      </c>
+      <c r="B8" s="5">
+        <f>Raw_Data_MR!B8</f>
+        <v/>
+      </c>
+      <c r="C8" s="5">
+        <f>IF(AND(B8&gt;cfg_mr_poa_threshold_wm2,B8&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="17">
+        <f>MEDIAN(Raw_Data_MR!D8,Raw_Data_MR!E8,Raw_Data_MR!F8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="17">
+        <f>MEDIAN(Raw_Data_MR!C8,Raw_Data_MR!E8,Raw_Data_MR!F8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="17">
+        <f>MEDIAN(Raw_Data_MR!C8,Raw_Data_MR!D8,Raw_Data_MR!F8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="17">
+        <f>MEDIAN(Raw_Data_MR!C8,Raw_Data_MR!D8,Raw_Data_MR!E8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="17">
+        <f>MEDIAN(Raw_Data_MR!H8,Raw_Data_MR!I8,Raw_Data_MR!J8,Raw_Data_MR!K8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="17">
+        <f>MEDIAN(Raw_Data_MR!G8,Raw_Data_MR!I8,Raw_Data_MR!J8,Raw_Data_MR!K8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="17">
+        <f>MEDIAN(Raw_Data_MR!G8,Raw_Data_MR!H8,Raw_Data_MR!J8,Raw_Data_MR!K8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="17">
+        <f>MEDIAN(Raw_Data_MR!G8,Raw_Data_MR!H8,Raw_Data_MR!I8,Raw_Data_MR!K8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="17">
+        <f>MEDIAN(Raw_Data_MR!G8,Raw_Data_MR!H8,Raw_Data_MR!I8,Raw_Data_MR!J8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="31">
+        <f>Raw_Data_MR!C8/MAX(D8,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N8" s="31">
+        <f>Raw_Data_MR!D8/MAX(E8,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O8" s="31">
+        <f>Raw_Data_MR!E8/MAX(F8,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P8" s="31">
+        <f>Raw_Data_MR!F8/MAX(G8,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="31">
+        <f>Raw_Data_MR!G8/MAX(H8,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R8" s="31">
+        <f>Raw_Data_MR!H8/MAX(I8,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S8" s="31">
+        <f>Raw_Data_MR!I8/MAX(J8,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T8" s="31">
+        <f>Raw_Data_MR!J8/MAX(K8,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U8" s="31">
+        <f>Raw_Data_MR!K8/MAX(L8,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V8" s="5">
+        <f>IF(AND(M8&lt;cfg_mr_ratio_threshold,$C8=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W8" s="5">
+        <f>IF(AND(N8&lt;cfg_mr_ratio_threshold,$C8=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X8" s="5">
+        <f>IF(AND(O8&lt;cfg_mr_ratio_threshold,$C8=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y8" s="5">
+        <f>IF(AND(P8&lt;cfg_mr_ratio_threshold,$C8=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z8" s="5">
+        <f>IF(AND(Q8&lt;cfg_mr_ratio_threshold,$C8=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA8" s="5">
+        <f>IF(AND(R8&lt;cfg_mr_ratio_threshold,$C8=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB8" s="5">
+        <f>IF(AND(S8&lt;cfg_mr_ratio_threshold,$C8=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC8" s="5">
+        <f>IF(AND(T8&lt;cfg_mr_ratio_threshold,$C8=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD8" s="5">
+        <f>IF(AND(U8&lt;cfg_mr_ratio_threshold,$C8=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE8" s="5">
+        <f>IF(V8=1,AE7+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF8" s="5">
+        <f>IF(W8=1,AF7+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG8" s="5">
+        <f>IF(X8=1,AG7+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH8" s="5">
+        <f>IF(Y8=1,AH7+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI8" s="5">
+        <f>IF(Z8=1,AI7+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="5">
+        <f>IF(AA8=1,AJ7+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK8" s="5">
+        <f>IF(AB8=1,AK7+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL8" s="5">
+        <f>IF(AC8=1,AL7+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM8" s="5">
+        <f>IF(AD8=1,AM7+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="40">
+        <f>Raw_Data_MR!A9</f>
+        <v/>
+      </c>
+      <c r="B9" s="5">
+        <f>Raw_Data_MR!B9</f>
+        <v/>
+      </c>
+      <c r="C9" s="5">
+        <f>IF(AND(B9&gt;cfg_mr_poa_threshold_wm2,B9&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="17">
+        <f>MEDIAN(Raw_Data_MR!D9,Raw_Data_MR!E9,Raw_Data_MR!F9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="17">
+        <f>MEDIAN(Raw_Data_MR!C9,Raw_Data_MR!E9,Raw_Data_MR!F9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="17">
+        <f>MEDIAN(Raw_Data_MR!C9,Raw_Data_MR!D9,Raw_Data_MR!F9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="17">
+        <f>MEDIAN(Raw_Data_MR!C9,Raw_Data_MR!D9,Raw_Data_MR!E9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="17">
+        <f>MEDIAN(Raw_Data_MR!H9,Raw_Data_MR!I9,Raw_Data_MR!J9,Raw_Data_MR!K9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="17">
+        <f>MEDIAN(Raw_Data_MR!G9,Raw_Data_MR!I9,Raw_Data_MR!J9,Raw_Data_MR!K9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="17">
+        <f>MEDIAN(Raw_Data_MR!G9,Raw_Data_MR!H9,Raw_Data_MR!J9,Raw_Data_MR!K9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="17">
+        <f>MEDIAN(Raw_Data_MR!G9,Raw_Data_MR!H9,Raw_Data_MR!I9,Raw_Data_MR!K9)</f>
+        <v/>
+      </c>
+      <c r="L9" s="17">
+        <f>MEDIAN(Raw_Data_MR!G9,Raw_Data_MR!H9,Raw_Data_MR!I9,Raw_Data_MR!J9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="31">
+        <f>Raw_Data_MR!C9/MAX(D9,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N9" s="31">
+        <f>Raw_Data_MR!D9/MAX(E9,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O9" s="31">
+        <f>Raw_Data_MR!E9/MAX(F9,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P9" s="31">
+        <f>Raw_Data_MR!F9/MAX(G9,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q9" s="31">
+        <f>Raw_Data_MR!G9/MAX(H9,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R9" s="31">
+        <f>Raw_Data_MR!H9/MAX(I9,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S9" s="31">
+        <f>Raw_Data_MR!I9/MAX(J9,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T9" s="31">
+        <f>Raw_Data_MR!J9/MAX(K9,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U9" s="31">
+        <f>Raw_Data_MR!K9/MAX(L9,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V9" s="5">
+        <f>IF(AND(M9&lt;cfg_mr_ratio_threshold,$C9=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W9" s="5">
+        <f>IF(AND(N9&lt;cfg_mr_ratio_threshold,$C9=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X9" s="5">
+        <f>IF(AND(O9&lt;cfg_mr_ratio_threshold,$C9=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y9" s="5">
+        <f>IF(AND(P9&lt;cfg_mr_ratio_threshold,$C9=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z9" s="5">
+        <f>IF(AND(Q9&lt;cfg_mr_ratio_threshold,$C9=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA9" s="5">
+        <f>IF(AND(R9&lt;cfg_mr_ratio_threshold,$C9=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB9" s="5">
+        <f>IF(AND(S9&lt;cfg_mr_ratio_threshold,$C9=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC9" s="5">
+        <f>IF(AND(T9&lt;cfg_mr_ratio_threshold,$C9=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD9" s="5">
+        <f>IF(AND(U9&lt;cfg_mr_ratio_threshold,$C9=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE9" s="5">
+        <f>IF(V9=1,AE8+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF9" s="5">
+        <f>IF(W9=1,AF8+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG9" s="5">
+        <f>IF(X9=1,AG8+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH9" s="5">
+        <f>IF(Y9=1,AH8+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI9" s="5">
+        <f>IF(Z9=1,AI8+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="5">
+        <f>IF(AA9=1,AJ8+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK9" s="5">
+        <f>IF(AB9=1,AK8+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL9" s="5">
+        <f>IF(AC9=1,AL8+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM9" s="5">
+        <f>IF(AD9=1,AM8+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="40">
+        <f>Raw_Data_MR!A10</f>
+        <v/>
+      </c>
+      <c r="B10" s="5">
+        <f>Raw_Data_MR!B10</f>
+        <v/>
+      </c>
+      <c r="C10" s="5">
+        <f>IF(AND(B10&gt;cfg_mr_poa_threshold_wm2,B10&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="17">
+        <f>MEDIAN(Raw_Data_MR!D10,Raw_Data_MR!E10,Raw_Data_MR!F10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="17">
+        <f>MEDIAN(Raw_Data_MR!C10,Raw_Data_MR!E10,Raw_Data_MR!F10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="17">
+        <f>MEDIAN(Raw_Data_MR!C10,Raw_Data_MR!D10,Raw_Data_MR!F10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="17">
+        <f>MEDIAN(Raw_Data_MR!C10,Raw_Data_MR!D10,Raw_Data_MR!E10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="17">
+        <f>MEDIAN(Raw_Data_MR!H10,Raw_Data_MR!I10,Raw_Data_MR!J10,Raw_Data_MR!K10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="17">
+        <f>MEDIAN(Raw_Data_MR!G10,Raw_Data_MR!I10,Raw_Data_MR!J10,Raw_Data_MR!K10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="17">
+        <f>MEDIAN(Raw_Data_MR!G10,Raw_Data_MR!H10,Raw_Data_MR!J10,Raw_Data_MR!K10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="17">
+        <f>MEDIAN(Raw_Data_MR!G10,Raw_Data_MR!H10,Raw_Data_MR!I10,Raw_Data_MR!K10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="17">
+        <f>MEDIAN(Raw_Data_MR!G10,Raw_Data_MR!H10,Raw_Data_MR!I10,Raw_Data_MR!J10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="31">
+        <f>Raw_Data_MR!C10/MAX(D10,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N10" s="31">
+        <f>Raw_Data_MR!D10/MAX(E10,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O10" s="31">
+        <f>Raw_Data_MR!E10/MAX(F10,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P10" s="31">
+        <f>Raw_Data_MR!F10/MAX(G10,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q10" s="31">
+        <f>Raw_Data_MR!G10/MAX(H10,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R10" s="31">
+        <f>Raw_Data_MR!H10/MAX(I10,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S10" s="31">
+        <f>Raw_Data_MR!I10/MAX(J10,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T10" s="31">
+        <f>Raw_Data_MR!J10/MAX(K10,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U10" s="31">
+        <f>Raw_Data_MR!K10/MAX(L10,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V10" s="5">
+        <f>IF(AND(M10&lt;cfg_mr_ratio_threshold,$C10=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W10" s="5">
+        <f>IF(AND(N10&lt;cfg_mr_ratio_threshold,$C10=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X10" s="5">
+        <f>IF(AND(O10&lt;cfg_mr_ratio_threshold,$C10=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y10" s="5">
+        <f>IF(AND(P10&lt;cfg_mr_ratio_threshold,$C10=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z10" s="5">
+        <f>IF(AND(Q10&lt;cfg_mr_ratio_threshold,$C10=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA10" s="5">
+        <f>IF(AND(R10&lt;cfg_mr_ratio_threshold,$C10=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB10" s="5">
+        <f>IF(AND(S10&lt;cfg_mr_ratio_threshold,$C10=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC10" s="5">
+        <f>IF(AND(T10&lt;cfg_mr_ratio_threshold,$C10=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD10" s="5">
+        <f>IF(AND(U10&lt;cfg_mr_ratio_threshold,$C10=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE10" s="5">
+        <f>IF(V10=1,AE9+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF10" s="5">
+        <f>IF(W10=1,AF9+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG10" s="5">
+        <f>IF(X10=1,AG9+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH10" s="5">
+        <f>IF(Y10=1,AH9+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI10" s="5">
+        <f>IF(Z10=1,AI9+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="5">
+        <f>IF(AA10=1,AJ9+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK10" s="5">
+        <f>IF(AB10=1,AK9+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL10" s="5">
+        <f>IF(AC10=1,AL9+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM10" s="5">
+        <f>IF(AD10=1,AM9+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="40">
+        <f>Raw_Data_MR!A11</f>
+        <v/>
+      </c>
+      <c r="B11" s="5">
+        <f>Raw_Data_MR!B11</f>
+        <v/>
+      </c>
+      <c r="C11" s="5">
+        <f>IF(AND(B11&gt;cfg_mr_poa_threshold_wm2,B11&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="17">
+        <f>MEDIAN(Raw_Data_MR!D11,Raw_Data_MR!E11,Raw_Data_MR!F11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="17">
+        <f>MEDIAN(Raw_Data_MR!C11,Raw_Data_MR!E11,Raw_Data_MR!F11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="17">
+        <f>MEDIAN(Raw_Data_MR!C11,Raw_Data_MR!D11,Raw_Data_MR!F11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="17">
+        <f>MEDIAN(Raw_Data_MR!C11,Raw_Data_MR!D11,Raw_Data_MR!E11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="17">
+        <f>MEDIAN(Raw_Data_MR!H11,Raw_Data_MR!I11,Raw_Data_MR!J11,Raw_Data_MR!K11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="17">
+        <f>MEDIAN(Raw_Data_MR!G11,Raw_Data_MR!I11,Raw_Data_MR!J11,Raw_Data_MR!K11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="17">
+        <f>MEDIAN(Raw_Data_MR!G11,Raw_Data_MR!H11,Raw_Data_MR!J11,Raw_Data_MR!K11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="17">
+        <f>MEDIAN(Raw_Data_MR!G11,Raw_Data_MR!H11,Raw_Data_MR!I11,Raw_Data_MR!K11)</f>
+        <v/>
+      </c>
+      <c r="L11" s="17">
+        <f>MEDIAN(Raw_Data_MR!G11,Raw_Data_MR!H11,Raw_Data_MR!I11,Raw_Data_MR!J11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="31">
+        <f>Raw_Data_MR!C11/MAX(D11,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N11" s="31">
+        <f>Raw_Data_MR!D11/MAX(E11,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O11" s="31">
+        <f>Raw_Data_MR!E11/MAX(F11,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P11" s="31">
+        <f>Raw_Data_MR!F11/MAX(G11,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q11" s="31">
+        <f>Raw_Data_MR!G11/MAX(H11,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R11" s="31">
+        <f>Raw_Data_MR!H11/MAX(I11,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S11" s="31">
+        <f>Raw_Data_MR!I11/MAX(J11,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T11" s="31">
+        <f>Raw_Data_MR!J11/MAX(K11,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U11" s="31">
+        <f>Raw_Data_MR!K11/MAX(L11,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V11" s="5">
+        <f>IF(AND(M11&lt;cfg_mr_ratio_threshold,$C11=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W11" s="5">
+        <f>IF(AND(N11&lt;cfg_mr_ratio_threshold,$C11=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X11" s="5">
+        <f>IF(AND(O11&lt;cfg_mr_ratio_threshold,$C11=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y11" s="5">
+        <f>IF(AND(P11&lt;cfg_mr_ratio_threshold,$C11=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z11" s="5">
+        <f>IF(AND(Q11&lt;cfg_mr_ratio_threshold,$C11=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA11" s="5">
+        <f>IF(AND(R11&lt;cfg_mr_ratio_threshold,$C11=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB11" s="5">
+        <f>IF(AND(S11&lt;cfg_mr_ratio_threshold,$C11=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC11" s="5">
+        <f>IF(AND(T11&lt;cfg_mr_ratio_threshold,$C11=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD11" s="5">
+        <f>IF(AND(U11&lt;cfg_mr_ratio_threshold,$C11=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE11" s="5">
+        <f>IF(V11=1,AE10+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF11" s="5">
+        <f>IF(W11=1,AF10+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG11" s="5">
+        <f>IF(X11=1,AG10+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH11" s="5">
+        <f>IF(Y11=1,AH10+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI11" s="5">
+        <f>IF(Z11=1,AI10+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="5">
+        <f>IF(AA11=1,AJ10+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK11" s="5">
+        <f>IF(AB11=1,AK10+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL11" s="5">
+        <f>IF(AC11=1,AL10+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM11" s="5">
+        <f>IF(AD11=1,AM10+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="40">
+        <f>Raw_Data_MR!A12</f>
+        <v/>
+      </c>
+      <c r="B12" s="5">
+        <f>Raw_Data_MR!B12</f>
+        <v/>
+      </c>
+      <c r="C12" s="5">
+        <f>IF(AND(B12&gt;cfg_mr_poa_threshold_wm2,B12&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="17">
+        <f>MEDIAN(Raw_Data_MR!D12,Raw_Data_MR!E12,Raw_Data_MR!F12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="17">
+        <f>MEDIAN(Raw_Data_MR!C12,Raw_Data_MR!E12,Raw_Data_MR!F12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="17">
+        <f>MEDIAN(Raw_Data_MR!C12,Raw_Data_MR!D12,Raw_Data_MR!F12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="17">
+        <f>MEDIAN(Raw_Data_MR!C12,Raw_Data_MR!D12,Raw_Data_MR!E12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="17">
+        <f>MEDIAN(Raw_Data_MR!H12,Raw_Data_MR!I12,Raw_Data_MR!J12,Raw_Data_MR!K12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="17">
+        <f>MEDIAN(Raw_Data_MR!G12,Raw_Data_MR!I12,Raw_Data_MR!J12,Raw_Data_MR!K12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="17">
+        <f>MEDIAN(Raw_Data_MR!G12,Raw_Data_MR!H12,Raw_Data_MR!J12,Raw_Data_MR!K12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="17">
+        <f>MEDIAN(Raw_Data_MR!G12,Raw_Data_MR!H12,Raw_Data_MR!I12,Raw_Data_MR!K12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="17">
+        <f>MEDIAN(Raw_Data_MR!G12,Raw_Data_MR!H12,Raw_Data_MR!I12,Raw_Data_MR!J12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="31">
+        <f>Raw_Data_MR!C12/MAX(D12,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N12" s="31">
+        <f>Raw_Data_MR!D12/MAX(E12,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O12" s="31">
+        <f>Raw_Data_MR!E12/MAX(F12,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P12" s="31">
+        <f>Raw_Data_MR!F12/MAX(G12,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="31">
+        <f>Raw_Data_MR!G12/MAX(H12,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R12" s="31">
+        <f>Raw_Data_MR!H12/MAX(I12,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S12" s="31">
+        <f>Raw_Data_MR!I12/MAX(J12,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T12" s="31">
+        <f>Raw_Data_MR!J12/MAX(K12,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U12" s="31">
+        <f>Raw_Data_MR!K12/MAX(L12,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V12" s="5">
+        <f>IF(AND(M12&lt;cfg_mr_ratio_threshold,$C12=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W12" s="5">
+        <f>IF(AND(N12&lt;cfg_mr_ratio_threshold,$C12=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X12" s="5">
+        <f>IF(AND(O12&lt;cfg_mr_ratio_threshold,$C12=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y12" s="5">
+        <f>IF(AND(P12&lt;cfg_mr_ratio_threshold,$C12=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z12" s="5">
+        <f>IF(AND(Q12&lt;cfg_mr_ratio_threshold,$C12=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA12" s="5">
+        <f>IF(AND(R12&lt;cfg_mr_ratio_threshold,$C12=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB12" s="5">
+        <f>IF(AND(S12&lt;cfg_mr_ratio_threshold,$C12=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC12" s="5">
+        <f>IF(AND(T12&lt;cfg_mr_ratio_threshold,$C12=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD12" s="5">
+        <f>IF(AND(U12&lt;cfg_mr_ratio_threshold,$C12=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE12" s="5">
+        <f>IF(V12=1,AE11+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF12" s="5">
+        <f>IF(W12=1,AF11+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG12" s="5">
+        <f>IF(X12=1,AG11+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH12" s="5">
+        <f>IF(Y12=1,AH11+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI12" s="5">
+        <f>IF(Z12=1,AI11+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="5">
+        <f>IF(AA12=1,AJ11+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK12" s="5">
+        <f>IF(AB12=1,AK11+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL12" s="5">
+        <f>IF(AC12=1,AL11+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM12" s="5">
+        <f>IF(AD12=1,AM11+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="40">
+        <f>Raw_Data_MR!A13</f>
+        <v/>
+      </c>
+      <c r="B13" s="5">
+        <f>Raw_Data_MR!B13</f>
+        <v/>
+      </c>
+      <c r="C13" s="5">
+        <f>IF(AND(B13&gt;cfg_mr_poa_threshold_wm2,B13&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="17">
+        <f>MEDIAN(Raw_Data_MR!D13,Raw_Data_MR!E13,Raw_Data_MR!F13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="17">
+        <f>MEDIAN(Raw_Data_MR!C13,Raw_Data_MR!E13,Raw_Data_MR!F13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="17">
+        <f>MEDIAN(Raw_Data_MR!C13,Raw_Data_MR!D13,Raw_Data_MR!F13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="17">
+        <f>MEDIAN(Raw_Data_MR!C13,Raw_Data_MR!D13,Raw_Data_MR!E13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="17">
+        <f>MEDIAN(Raw_Data_MR!H13,Raw_Data_MR!I13,Raw_Data_MR!J13,Raw_Data_MR!K13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="17">
+        <f>MEDIAN(Raw_Data_MR!G13,Raw_Data_MR!I13,Raw_Data_MR!J13,Raw_Data_MR!K13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="17">
+        <f>MEDIAN(Raw_Data_MR!G13,Raw_Data_MR!H13,Raw_Data_MR!J13,Raw_Data_MR!K13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="17">
+        <f>MEDIAN(Raw_Data_MR!G13,Raw_Data_MR!H13,Raw_Data_MR!I13,Raw_Data_MR!K13)</f>
+        <v/>
+      </c>
+      <c r="L13" s="17">
+        <f>MEDIAN(Raw_Data_MR!G13,Raw_Data_MR!H13,Raw_Data_MR!I13,Raw_Data_MR!J13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="31">
+        <f>Raw_Data_MR!C13/MAX(D13,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N13" s="31">
+        <f>Raw_Data_MR!D13/MAX(E13,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O13" s="31">
+        <f>Raw_Data_MR!E13/MAX(F13,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P13" s="31">
+        <f>Raw_Data_MR!F13/MAX(G13,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q13" s="31">
+        <f>Raw_Data_MR!G13/MAX(H13,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R13" s="31">
+        <f>Raw_Data_MR!H13/MAX(I13,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S13" s="31">
+        <f>Raw_Data_MR!I13/MAX(J13,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T13" s="31">
+        <f>Raw_Data_MR!J13/MAX(K13,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U13" s="31">
+        <f>Raw_Data_MR!K13/MAX(L13,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V13" s="5">
+        <f>IF(AND(M13&lt;cfg_mr_ratio_threshold,$C13=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W13" s="5">
+        <f>IF(AND(N13&lt;cfg_mr_ratio_threshold,$C13=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X13" s="5">
+        <f>IF(AND(O13&lt;cfg_mr_ratio_threshold,$C13=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y13" s="5">
+        <f>IF(AND(P13&lt;cfg_mr_ratio_threshold,$C13=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z13" s="5">
+        <f>IF(AND(Q13&lt;cfg_mr_ratio_threshold,$C13=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA13" s="5">
+        <f>IF(AND(R13&lt;cfg_mr_ratio_threshold,$C13=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB13" s="5">
+        <f>IF(AND(S13&lt;cfg_mr_ratio_threshold,$C13=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC13" s="5">
+        <f>IF(AND(T13&lt;cfg_mr_ratio_threshold,$C13=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD13" s="5">
+        <f>IF(AND(U13&lt;cfg_mr_ratio_threshold,$C13=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE13" s="5">
+        <f>IF(V13=1,AE12+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF13" s="5">
+        <f>IF(W13=1,AF12+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG13" s="5">
+        <f>IF(X13=1,AG12+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH13" s="5">
+        <f>IF(Y13=1,AH12+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI13" s="5">
+        <f>IF(Z13=1,AI12+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="5">
+        <f>IF(AA13=1,AJ12+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK13" s="5">
+        <f>IF(AB13=1,AK12+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL13" s="5">
+        <f>IF(AC13=1,AL12+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM13" s="5">
+        <f>IF(AD13=1,AM12+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40">
+        <f>Raw_Data_MR!A14</f>
+        <v/>
+      </c>
+      <c r="B14" s="5">
+        <f>Raw_Data_MR!B14</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IF(AND(B14&gt;cfg_mr_poa_threshold_wm2,B14&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D14" s="17">
+        <f>MEDIAN(Raw_Data_MR!D14,Raw_Data_MR!E14,Raw_Data_MR!F14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="17">
+        <f>MEDIAN(Raw_Data_MR!C14,Raw_Data_MR!E14,Raw_Data_MR!F14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="17">
+        <f>MEDIAN(Raw_Data_MR!C14,Raw_Data_MR!D14,Raw_Data_MR!F14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="17">
+        <f>MEDIAN(Raw_Data_MR!C14,Raw_Data_MR!D14,Raw_Data_MR!E14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="17">
+        <f>MEDIAN(Raw_Data_MR!H14,Raw_Data_MR!I14,Raw_Data_MR!J14,Raw_Data_MR!K14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="17">
+        <f>MEDIAN(Raw_Data_MR!G14,Raw_Data_MR!I14,Raw_Data_MR!J14,Raw_Data_MR!K14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="17">
+        <f>MEDIAN(Raw_Data_MR!G14,Raw_Data_MR!H14,Raw_Data_MR!J14,Raw_Data_MR!K14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="17">
+        <f>MEDIAN(Raw_Data_MR!G14,Raw_Data_MR!H14,Raw_Data_MR!I14,Raw_Data_MR!K14)</f>
+        <v/>
+      </c>
+      <c r="L14" s="17">
+        <f>MEDIAN(Raw_Data_MR!G14,Raw_Data_MR!H14,Raw_Data_MR!I14,Raw_Data_MR!J14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="31">
+        <f>Raw_Data_MR!C14/MAX(D14,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N14" s="31">
+        <f>Raw_Data_MR!D14/MAX(E14,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O14" s="31">
+        <f>Raw_Data_MR!E14/MAX(F14,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P14" s="31">
+        <f>Raw_Data_MR!F14/MAX(G14,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="31">
+        <f>Raw_Data_MR!G14/MAX(H14,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R14" s="31">
+        <f>Raw_Data_MR!H14/MAX(I14,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S14" s="31">
+        <f>Raw_Data_MR!I14/MAX(J14,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T14" s="31">
+        <f>Raw_Data_MR!J14/MAX(K14,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U14" s="31">
+        <f>Raw_Data_MR!K14/MAX(L14,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V14" s="5">
+        <f>IF(AND(M14&lt;cfg_mr_ratio_threshold,$C14=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W14" s="5">
+        <f>IF(AND(N14&lt;cfg_mr_ratio_threshold,$C14=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X14" s="5">
+        <f>IF(AND(O14&lt;cfg_mr_ratio_threshold,$C14=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y14" s="5">
+        <f>IF(AND(P14&lt;cfg_mr_ratio_threshold,$C14=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z14" s="5">
+        <f>IF(AND(Q14&lt;cfg_mr_ratio_threshold,$C14=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA14" s="5">
+        <f>IF(AND(R14&lt;cfg_mr_ratio_threshold,$C14=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB14" s="5">
+        <f>IF(AND(S14&lt;cfg_mr_ratio_threshold,$C14=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC14" s="5">
+        <f>IF(AND(T14&lt;cfg_mr_ratio_threshold,$C14=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD14" s="5">
+        <f>IF(AND(U14&lt;cfg_mr_ratio_threshold,$C14=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE14" s="5">
+        <f>IF(V14=1,AE13+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF14" s="5">
+        <f>IF(W14=1,AF13+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG14" s="5">
+        <f>IF(X14=1,AG13+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH14" s="5">
+        <f>IF(Y14=1,AH13+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI14" s="5">
+        <f>IF(Z14=1,AI13+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="5">
+        <f>IF(AA14=1,AJ13+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK14" s="5">
+        <f>IF(AB14=1,AK13+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL14" s="5">
+        <f>IF(AC14=1,AL13+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM14" s="5">
+        <f>IF(AD14=1,AM13+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="40">
+        <f>Raw_Data_MR!A15</f>
+        <v/>
+      </c>
+      <c r="B15" s="5">
+        <f>Raw_Data_MR!B15</f>
+        <v/>
+      </c>
+      <c r="C15" s="5">
+        <f>IF(AND(B15&gt;cfg_mr_poa_threshold_wm2,B15&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="17">
+        <f>MEDIAN(Raw_Data_MR!D15,Raw_Data_MR!E15,Raw_Data_MR!F15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="17">
+        <f>MEDIAN(Raw_Data_MR!C15,Raw_Data_MR!E15,Raw_Data_MR!F15)</f>
+        <v/>
+      </c>
+      <c r="F15" s="17">
+        <f>MEDIAN(Raw_Data_MR!C15,Raw_Data_MR!D15,Raw_Data_MR!F15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="17">
+        <f>MEDIAN(Raw_Data_MR!C15,Raw_Data_MR!D15,Raw_Data_MR!E15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="17">
+        <f>MEDIAN(Raw_Data_MR!H15,Raw_Data_MR!I15,Raw_Data_MR!J15,Raw_Data_MR!K15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="17">
+        <f>MEDIAN(Raw_Data_MR!G15,Raw_Data_MR!I15,Raw_Data_MR!J15,Raw_Data_MR!K15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="17">
+        <f>MEDIAN(Raw_Data_MR!G15,Raw_Data_MR!H15,Raw_Data_MR!J15,Raw_Data_MR!K15)</f>
+        <v/>
+      </c>
+      <c r="K15" s="17">
+        <f>MEDIAN(Raw_Data_MR!G15,Raw_Data_MR!H15,Raw_Data_MR!I15,Raw_Data_MR!K15)</f>
+        <v/>
+      </c>
+      <c r="L15" s="17">
+        <f>MEDIAN(Raw_Data_MR!G15,Raw_Data_MR!H15,Raw_Data_MR!I15,Raw_Data_MR!J15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="31">
+        <f>Raw_Data_MR!C15/MAX(D15,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N15" s="31">
+        <f>Raw_Data_MR!D15/MAX(E15,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O15" s="31">
+        <f>Raw_Data_MR!E15/MAX(F15,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P15" s="31">
+        <f>Raw_Data_MR!F15/MAX(G15,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q15" s="31">
+        <f>Raw_Data_MR!G15/MAX(H15,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R15" s="31">
+        <f>Raw_Data_MR!H15/MAX(I15,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S15" s="31">
+        <f>Raw_Data_MR!I15/MAX(J15,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T15" s="31">
+        <f>Raw_Data_MR!J15/MAX(K15,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U15" s="31">
+        <f>Raw_Data_MR!K15/MAX(L15,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V15" s="5">
+        <f>IF(AND(M15&lt;cfg_mr_ratio_threshold,$C15=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W15" s="5">
+        <f>IF(AND(N15&lt;cfg_mr_ratio_threshold,$C15=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X15" s="5">
+        <f>IF(AND(O15&lt;cfg_mr_ratio_threshold,$C15=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y15" s="5">
+        <f>IF(AND(P15&lt;cfg_mr_ratio_threshold,$C15=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z15" s="5">
+        <f>IF(AND(Q15&lt;cfg_mr_ratio_threshold,$C15=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA15" s="5">
+        <f>IF(AND(R15&lt;cfg_mr_ratio_threshold,$C15=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB15" s="5">
+        <f>IF(AND(S15&lt;cfg_mr_ratio_threshold,$C15=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC15" s="5">
+        <f>IF(AND(T15&lt;cfg_mr_ratio_threshold,$C15=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD15" s="5">
+        <f>IF(AND(U15&lt;cfg_mr_ratio_threshold,$C15=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE15" s="5">
+        <f>IF(V15=1,AE14+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF15" s="5">
+        <f>IF(W15=1,AF14+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG15" s="5">
+        <f>IF(X15=1,AG14+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH15" s="5">
+        <f>IF(Y15=1,AH14+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI15" s="5">
+        <f>IF(Z15=1,AI14+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="5">
+        <f>IF(AA15=1,AJ14+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK15" s="5">
+        <f>IF(AB15=1,AK14+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL15" s="5">
+        <f>IF(AC15=1,AL14+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM15" s="5">
+        <f>IF(AD15=1,AM14+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="40">
+        <f>Raw_Data_MR!A16</f>
+        <v/>
+      </c>
+      <c r="B16" s="5">
+        <f>Raw_Data_MR!B16</f>
+        <v/>
+      </c>
+      <c r="C16" s="5">
+        <f>IF(AND(B16&gt;cfg_mr_poa_threshold_wm2,B16&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="17">
+        <f>MEDIAN(Raw_Data_MR!D16,Raw_Data_MR!E16,Raw_Data_MR!F16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="17">
+        <f>MEDIAN(Raw_Data_MR!C16,Raw_Data_MR!E16,Raw_Data_MR!F16)</f>
+        <v/>
+      </c>
+      <c r="F16" s="17">
+        <f>MEDIAN(Raw_Data_MR!C16,Raw_Data_MR!D16,Raw_Data_MR!F16)</f>
+        <v/>
+      </c>
+      <c r="G16" s="17">
+        <f>MEDIAN(Raw_Data_MR!C16,Raw_Data_MR!D16,Raw_Data_MR!E16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="17">
+        <f>MEDIAN(Raw_Data_MR!H16,Raw_Data_MR!I16,Raw_Data_MR!J16,Raw_Data_MR!K16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="17">
+        <f>MEDIAN(Raw_Data_MR!G16,Raw_Data_MR!I16,Raw_Data_MR!J16,Raw_Data_MR!K16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="17">
+        <f>MEDIAN(Raw_Data_MR!G16,Raw_Data_MR!H16,Raw_Data_MR!J16,Raw_Data_MR!K16)</f>
+        <v/>
+      </c>
+      <c r="K16" s="17">
+        <f>MEDIAN(Raw_Data_MR!G16,Raw_Data_MR!H16,Raw_Data_MR!I16,Raw_Data_MR!K16)</f>
+        <v/>
+      </c>
+      <c r="L16" s="17">
+        <f>MEDIAN(Raw_Data_MR!G16,Raw_Data_MR!H16,Raw_Data_MR!I16,Raw_Data_MR!J16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="31">
+        <f>Raw_Data_MR!C16/MAX(D16,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N16" s="31">
+        <f>Raw_Data_MR!D16/MAX(E16,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O16" s="31">
+        <f>Raw_Data_MR!E16/MAX(F16,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P16" s="31">
+        <f>Raw_Data_MR!F16/MAX(G16,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q16" s="31">
+        <f>Raw_Data_MR!G16/MAX(H16,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R16" s="31">
+        <f>Raw_Data_MR!H16/MAX(I16,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S16" s="31">
+        <f>Raw_Data_MR!I16/MAX(J16,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T16" s="31">
+        <f>Raw_Data_MR!J16/MAX(K16,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U16" s="31">
+        <f>Raw_Data_MR!K16/MAX(L16,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V16" s="5">
+        <f>IF(AND(M16&lt;cfg_mr_ratio_threshold,$C16=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W16" s="5">
+        <f>IF(AND(N16&lt;cfg_mr_ratio_threshold,$C16=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X16" s="5">
+        <f>IF(AND(O16&lt;cfg_mr_ratio_threshold,$C16=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y16" s="5">
+        <f>IF(AND(P16&lt;cfg_mr_ratio_threshold,$C16=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z16" s="5">
+        <f>IF(AND(Q16&lt;cfg_mr_ratio_threshold,$C16=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA16" s="5">
+        <f>IF(AND(R16&lt;cfg_mr_ratio_threshold,$C16=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB16" s="5">
+        <f>IF(AND(S16&lt;cfg_mr_ratio_threshold,$C16=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC16" s="5">
+        <f>IF(AND(T16&lt;cfg_mr_ratio_threshold,$C16=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD16" s="5">
+        <f>IF(AND(U16&lt;cfg_mr_ratio_threshold,$C16=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE16" s="5">
+        <f>IF(V16=1,AE15+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF16" s="5">
+        <f>IF(W16=1,AF15+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG16" s="5">
+        <f>IF(X16=1,AG15+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH16" s="5">
+        <f>IF(Y16=1,AH15+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI16" s="5">
+        <f>IF(Z16=1,AI15+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="5">
+        <f>IF(AA16=1,AJ15+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK16" s="5">
+        <f>IF(AB16=1,AK15+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL16" s="5">
+        <f>IF(AC16=1,AL15+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM16" s="5">
+        <f>IF(AD16=1,AM15+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="40">
+        <f>Raw_Data_MR!A17</f>
+        <v/>
+      </c>
+      <c r="B17" s="5">
+        <f>Raw_Data_MR!B17</f>
+        <v/>
+      </c>
+      <c r="C17" s="5">
+        <f>IF(AND(B17&gt;cfg_mr_poa_threshold_wm2,B17&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="17">
+        <f>MEDIAN(Raw_Data_MR!D17,Raw_Data_MR!E17,Raw_Data_MR!F17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="17">
+        <f>MEDIAN(Raw_Data_MR!C17,Raw_Data_MR!E17,Raw_Data_MR!F17)</f>
+        <v/>
+      </c>
+      <c r="F17" s="17">
+        <f>MEDIAN(Raw_Data_MR!C17,Raw_Data_MR!D17,Raw_Data_MR!F17)</f>
+        <v/>
+      </c>
+      <c r="G17" s="17">
+        <f>MEDIAN(Raw_Data_MR!C17,Raw_Data_MR!D17,Raw_Data_MR!E17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="17">
+        <f>MEDIAN(Raw_Data_MR!H17,Raw_Data_MR!I17,Raw_Data_MR!J17,Raw_Data_MR!K17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="17">
+        <f>MEDIAN(Raw_Data_MR!G17,Raw_Data_MR!I17,Raw_Data_MR!J17,Raw_Data_MR!K17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="17">
+        <f>MEDIAN(Raw_Data_MR!G17,Raw_Data_MR!H17,Raw_Data_MR!J17,Raw_Data_MR!K17)</f>
+        <v/>
+      </c>
+      <c r="K17" s="17">
+        <f>MEDIAN(Raw_Data_MR!G17,Raw_Data_MR!H17,Raw_Data_MR!I17,Raw_Data_MR!K17)</f>
+        <v/>
+      </c>
+      <c r="L17" s="17">
+        <f>MEDIAN(Raw_Data_MR!G17,Raw_Data_MR!H17,Raw_Data_MR!I17,Raw_Data_MR!J17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="31">
+        <f>Raw_Data_MR!C17/MAX(D17,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N17" s="31">
+        <f>Raw_Data_MR!D17/MAX(E17,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O17" s="31">
+        <f>Raw_Data_MR!E17/MAX(F17,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P17" s="31">
+        <f>Raw_Data_MR!F17/MAX(G17,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q17" s="31">
+        <f>Raw_Data_MR!G17/MAX(H17,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R17" s="31">
+        <f>Raw_Data_MR!H17/MAX(I17,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S17" s="31">
+        <f>Raw_Data_MR!I17/MAX(J17,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T17" s="31">
+        <f>Raw_Data_MR!J17/MAX(K17,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U17" s="31">
+        <f>Raw_Data_MR!K17/MAX(L17,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V17" s="5">
+        <f>IF(AND(M17&lt;cfg_mr_ratio_threshold,$C17=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W17" s="5">
+        <f>IF(AND(N17&lt;cfg_mr_ratio_threshold,$C17=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X17" s="5">
+        <f>IF(AND(O17&lt;cfg_mr_ratio_threshold,$C17=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y17" s="5">
+        <f>IF(AND(P17&lt;cfg_mr_ratio_threshold,$C17=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z17" s="5">
+        <f>IF(AND(Q17&lt;cfg_mr_ratio_threshold,$C17=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA17" s="5">
+        <f>IF(AND(R17&lt;cfg_mr_ratio_threshold,$C17=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB17" s="5">
+        <f>IF(AND(S17&lt;cfg_mr_ratio_threshold,$C17=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC17" s="5">
+        <f>IF(AND(T17&lt;cfg_mr_ratio_threshold,$C17=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD17" s="5">
+        <f>IF(AND(U17&lt;cfg_mr_ratio_threshold,$C17=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE17" s="5">
+        <f>IF(V17=1,AE16+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF17" s="5">
+        <f>IF(W17=1,AF16+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG17" s="5">
+        <f>IF(X17=1,AG16+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH17" s="5">
+        <f>IF(Y17=1,AH16+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI17" s="5">
+        <f>IF(Z17=1,AI16+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ17" s="5">
+        <f>IF(AA17=1,AJ16+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK17" s="5">
+        <f>IF(AB17=1,AK16+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL17" s="5">
+        <f>IF(AC17=1,AL16+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM17" s="5">
+        <f>IF(AD17=1,AM16+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="40">
+        <f>Raw_Data_MR!A18</f>
+        <v/>
+      </c>
+      <c r="B18" s="5">
+        <f>Raw_Data_MR!B18</f>
+        <v/>
+      </c>
+      <c r="C18" s="5">
+        <f>IF(AND(B18&gt;cfg_mr_poa_threshold_wm2,B18&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="17">
+        <f>MEDIAN(Raw_Data_MR!D18,Raw_Data_MR!E18,Raw_Data_MR!F18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="17">
+        <f>MEDIAN(Raw_Data_MR!C18,Raw_Data_MR!E18,Raw_Data_MR!F18)</f>
+        <v/>
+      </c>
+      <c r="F18" s="17">
+        <f>MEDIAN(Raw_Data_MR!C18,Raw_Data_MR!D18,Raw_Data_MR!F18)</f>
+        <v/>
+      </c>
+      <c r="G18" s="17">
+        <f>MEDIAN(Raw_Data_MR!C18,Raw_Data_MR!D18,Raw_Data_MR!E18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="17">
+        <f>MEDIAN(Raw_Data_MR!H18,Raw_Data_MR!I18,Raw_Data_MR!J18,Raw_Data_MR!K18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="17">
+        <f>MEDIAN(Raw_Data_MR!G18,Raw_Data_MR!I18,Raw_Data_MR!J18,Raw_Data_MR!K18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="17">
+        <f>MEDIAN(Raw_Data_MR!G18,Raw_Data_MR!H18,Raw_Data_MR!J18,Raw_Data_MR!K18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="17">
+        <f>MEDIAN(Raw_Data_MR!G18,Raw_Data_MR!H18,Raw_Data_MR!I18,Raw_Data_MR!K18)</f>
+        <v/>
+      </c>
+      <c r="L18" s="17">
+        <f>MEDIAN(Raw_Data_MR!G18,Raw_Data_MR!H18,Raw_Data_MR!I18,Raw_Data_MR!J18)</f>
+        <v/>
+      </c>
+      <c r="M18" s="31">
+        <f>Raw_Data_MR!C18/MAX(D18,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N18" s="31">
+        <f>Raw_Data_MR!D18/MAX(E18,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O18" s="31">
+        <f>Raw_Data_MR!E18/MAX(F18,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P18" s="31">
+        <f>Raw_Data_MR!F18/MAX(G18,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q18" s="31">
+        <f>Raw_Data_MR!G18/MAX(H18,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R18" s="31">
+        <f>Raw_Data_MR!H18/MAX(I18,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S18" s="31">
+        <f>Raw_Data_MR!I18/MAX(J18,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T18" s="31">
+        <f>Raw_Data_MR!J18/MAX(K18,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U18" s="31">
+        <f>Raw_Data_MR!K18/MAX(L18,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V18" s="5">
+        <f>IF(AND(M18&lt;cfg_mr_ratio_threshold,$C18=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W18" s="5">
+        <f>IF(AND(N18&lt;cfg_mr_ratio_threshold,$C18=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X18" s="5">
+        <f>IF(AND(O18&lt;cfg_mr_ratio_threshold,$C18=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y18" s="5">
+        <f>IF(AND(P18&lt;cfg_mr_ratio_threshold,$C18=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z18" s="5">
+        <f>IF(AND(Q18&lt;cfg_mr_ratio_threshold,$C18=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA18" s="5">
+        <f>IF(AND(R18&lt;cfg_mr_ratio_threshold,$C18=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB18" s="5">
+        <f>IF(AND(S18&lt;cfg_mr_ratio_threshold,$C18=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC18" s="5">
+        <f>IF(AND(T18&lt;cfg_mr_ratio_threshold,$C18=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD18" s="5">
+        <f>IF(AND(U18&lt;cfg_mr_ratio_threshold,$C18=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE18" s="5">
+        <f>IF(V18=1,AE17+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF18" s="5">
+        <f>IF(W18=1,AF17+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG18" s="5">
+        <f>IF(X18=1,AG17+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH18" s="5">
+        <f>IF(Y18=1,AH17+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI18" s="5">
+        <f>IF(Z18=1,AI17+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ18" s="5">
+        <f>IF(AA18=1,AJ17+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK18" s="5">
+        <f>IF(AB18=1,AK17+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL18" s="5">
+        <f>IF(AC18=1,AL17+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM18" s="5">
+        <f>IF(AD18=1,AM17+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="40">
+        <f>Raw_Data_MR!A19</f>
+        <v/>
+      </c>
+      <c r="B19" s="5">
+        <f>Raw_Data_MR!B19</f>
+        <v/>
+      </c>
+      <c r="C19" s="5">
+        <f>IF(AND(B19&gt;cfg_mr_poa_threshold_wm2,B19&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D19" s="17">
+        <f>MEDIAN(Raw_Data_MR!D19,Raw_Data_MR!E19,Raw_Data_MR!F19)</f>
+        <v/>
+      </c>
+      <c r="E19" s="17">
+        <f>MEDIAN(Raw_Data_MR!C19,Raw_Data_MR!E19,Raw_Data_MR!F19)</f>
+        <v/>
+      </c>
+      <c r="F19" s="17">
+        <f>MEDIAN(Raw_Data_MR!C19,Raw_Data_MR!D19,Raw_Data_MR!F19)</f>
+        <v/>
+      </c>
+      <c r="G19" s="17">
+        <f>MEDIAN(Raw_Data_MR!C19,Raw_Data_MR!D19,Raw_Data_MR!E19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="17">
+        <f>MEDIAN(Raw_Data_MR!H19,Raw_Data_MR!I19,Raw_Data_MR!J19,Raw_Data_MR!K19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="17">
+        <f>MEDIAN(Raw_Data_MR!G19,Raw_Data_MR!I19,Raw_Data_MR!J19,Raw_Data_MR!K19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="17">
+        <f>MEDIAN(Raw_Data_MR!G19,Raw_Data_MR!H19,Raw_Data_MR!J19,Raw_Data_MR!K19)</f>
+        <v/>
+      </c>
+      <c r="K19" s="17">
+        <f>MEDIAN(Raw_Data_MR!G19,Raw_Data_MR!H19,Raw_Data_MR!I19,Raw_Data_MR!K19)</f>
+        <v/>
+      </c>
+      <c r="L19" s="17">
+        <f>MEDIAN(Raw_Data_MR!G19,Raw_Data_MR!H19,Raw_Data_MR!I19,Raw_Data_MR!J19)</f>
+        <v/>
+      </c>
+      <c r="M19" s="31">
+        <f>Raw_Data_MR!C19/MAX(D19,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N19" s="31">
+        <f>Raw_Data_MR!D19/MAX(E19,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O19" s="31">
+        <f>Raw_Data_MR!E19/MAX(F19,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P19" s="31">
+        <f>Raw_Data_MR!F19/MAX(G19,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q19" s="31">
+        <f>Raw_Data_MR!G19/MAX(H19,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R19" s="31">
+        <f>Raw_Data_MR!H19/MAX(I19,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S19" s="31">
+        <f>Raw_Data_MR!I19/MAX(J19,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T19" s="31">
+        <f>Raw_Data_MR!J19/MAX(K19,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U19" s="31">
+        <f>Raw_Data_MR!K19/MAX(L19,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V19" s="5">
+        <f>IF(AND(M19&lt;cfg_mr_ratio_threshold,$C19=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W19" s="5">
+        <f>IF(AND(N19&lt;cfg_mr_ratio_threshold,$C19=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X19" s="5">
+        <f>IF(AND(O19&lt;cfg_mr_ratio_threshold,$C19=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y19" s="5">
+        <f>IF(AND(P19&lt;cfg_mr_ratio_threshold,$C19=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z19" s="5">
+        <f>IF(AND(Q19&lt;cfg_mr_ratio_threshold,$C19=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA19" s="5">
+        <f>IF(AND(R19&lt;cfg_mr_ratio_threshold,$C19=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB19" s="5">
+        <f>IF(AND(S19&lt;cfg_mr_ratio_threshold,$C19=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC19" s="5">
+        <f>IF(AND(T19&lt;cfg_mr_ratio_threshold,$C19=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD19" s="5">
+        <f>IF(AND(U19&lt;cfg_mr_ratio_threshold,$C19=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE19" s="5">
+        <f>IF(V19=1,AE18+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF19" s="5">
+        <f>IF(W19=1,AF18+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG19" s="5">
+        <f>IF(X19=1,AG18+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH19" s="5">
+        <f>IF(Y19=1,AH18+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI19" s="5">
+        <f>IF(Z19=1,AI18+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="5">
+        <f>IF(AA19=1,AJ18+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK19" s="5">
+        <f>IF(AB19=1,AK18+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL19" s="5">
+        <f>IF(AC19=1,AL18+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM19" s="5">
+        <f>IF(AD19=1,AM18+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="40">
+        <f>Raw_Data_MR!A20</f>
+        <v/>
+      </c>
+      <c r="B20" s="5">
+        <f>Raw_Data_MR!B20</f>
+        <v/>
+      </c>
+      <c r="C20" s="5">
+        <f>IF(AND(B20&gt;cfg_mr_poa_threshold_wm2,B20&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="17">
+        <f>MEDIAN(Raw_Data_MR!D20,Raw_Data_MR!E20,Raw_Data_MR!F20)</f>
+        <v/>
+      </c>
+      <c r="E20" s="17">
+        <f>MEDIAN(Raw_Data_MR!C20,Raw_Data_MR!E20,Raw_Data_MR!F20)</f>
+        <v/>
+      </c>
+      <c r="F20" s="17">
+        <f>MEDIAN(Raw_Data_MR!C20,Raw_Data_MR!D20,Raw_Data_MR!F20)</f>
+        <v/>
+      </c>
+      <c r="G20" s="17">
+        <f>MEDIAN(Raw_Data_MR!C20,Raw_Data_MR!D20,Raw_Data_MR!E20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="17">
+        <f>MEDIAN(Raw_Data_MR!H20,Raw_Data_MR!I20,Raw_Data_MR!J20,Raw_Data_MR!K20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="17">
+        <f>MEDIAN(Raw_Data_MR!G20,Raw_Data_MR!I20,Raw_Data_MR!J20,Raw_Data_MR!K20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="17">
+        <f>MEDIAN(Raw_Data_MR!G20,Raw_Data_MR!H20,Raw_Data_MR!J20,Raw_Data_MR!K20)</f>
+        <v/>
+      </c>
+      <c r="K20" s="17">
+        <f>MEDIAN(Raw_Data_MR!G20,Raw_Data_MR!H20,Raw_Data_MR!I20,Raw_Data_MR!K20)</f>
+        <v/>
+      </c>
+      <c r="L20" s="17">
+        <f>MEDIAN(Raw_Data_MR!G20,Raw_Data_MR!H20,Raw_Data_MR!I20,Raw_Data_MR!J20)</f>
+        <v/>
+      </c>
+      <c r="M20" s="31">
+        <f>Raw_Data_MR!C20/MAX(D20,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N20" s="31">
+        <f>Raw_Data_MR!D20/MAX(E20,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O20" s="31">
+        <f>Raw_Data_MR!E20/MAX(F20,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P20" s="31">
+        <f>Raw_Data_MR!F20/MAX(G20,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="31">
+        <f>Raw_Data_MR!G20/MAX(H20,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R20" s="31">
+        <f>Raw_Data_MR!H20/MAX(I20,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S20" s="31">
+        <f>Raw_Data_MR!I20/MAX(J20,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T20" s="31">
+        <f>Raw_Data_MR!J20/MAX(K20,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U20" s="31">
+        <f>Raw_Data_MR!K20/MAX(L20,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V20" s="5">
+        <f>IF(AND(M20&lt;cfg_mr_ratio_threshold,$C20=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W20" s="5">
+        <f>IF(AND(N20&lt;cfg_mr_ratio_threshold,$C20=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X20" s="5">
+        <f>IF(AND(O20&lt;cfg_mr_ratio_threshold,$C20=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y20" s="5">
+        <f>IF(AND(P20&lt;cfg_mr_ratio_threshold,$C20=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z20" s="5">
+        <f>IF(AND(Q20&lt;cfg_mr_ratio_threshold,$C20=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA20" s="5">
+        <f>IF(AND(R20&lt;cfg_mr_ratio_threshold,$C20=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB20" s="5">
+        <f>IF(AND(S20&lt;cfg_mr_ratio_threshold,$C20=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC20" s="5">
+        <f>IF(AND(T20&lt;cfg_mr_ratio_threshold,$C20=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD20" s="5">
+        <f>IF(AND(U20&lt;cfg_mr_ratio_threshold,$C20=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE20" s="5">
+        <f>IF(V20=1,AE19+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF20" s="5">
+        <f>IF(W20=1,AF19+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG20" s="5">
+        <f>IF(X20=1,AG19+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH20" s="5">
+        <f>IF(Y20=1,AH19+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI20" s="5">
+        <f>IF(Z20=1,AI19+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="5">
+        <f>IF(AA20=1,AJ19+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK20" s="5">
+        <f>IF(AB20=1,AK19+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL20" s="5">
+        <f>IF(AC20=1,AL19+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM20" s="5">
+        <f>IF(AD20=1,AM19+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="40">
+        <f>Raw_Data_MR!A21</f>
+        <v/>
+      </c>
+      <c r="B21" s="5">
+        <f>Raw_Data_MR!B21</f>
+        <v/>
+      </c>
+      <c r="C21" s="5">
+        <f>IF(AND(B21&gt;cfg_mr_poa_threshold_wm2,B21&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D21" s="17">
+        <f>MEDIAN(Raw_Data_MR!D21,Raw_Data_MR!E21,Raw_Data_MR!F21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="17">
+        <f>MEDIAN(Raw_Data_MR!C21,Raw_Data_MR!E21,Raw_Data_MR!F21)</f>
+        <v/>
+      </c>
+      <c r="F21" s="17">
+        <f>MEDIAN(Raw_Data_MR!C21,Raw_Data_MR!D21,Raw_Data_MR!F21)</f>
+        <v/>
+      </c>
+      <c r="G21" s="17">
+        <f>MEDIAN(Raw_Data_MR!C21,Raw_Data_MR!D21,Raw_Data_MR!E21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="17">
+        <f>MEDIAN(Raw_Data_MR!H21,Raw_Data_MR!I21,Raw_Data_MR!J21,Raw_Data_MR!K21)</f>
+        <v/>
+      </c>
+      <c r="I21" s="17">
+        <f>MEDIAN(Raw_Data_MR!G21,Raw_Data_MR!I21,Raw_Data_MR!J21,Raw_Data_MR!K21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="17">
+        <f>MEDIAN(Raw_Data_MR!G21,Raw_Data_MR!H21,Raw_Data_MR!J21,Raw_Data_MR!K21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="17">
+        <f>MEDIAN(Raw_Data_MR!G21,Raw_Data_MR!H21,Raw_Data_MR!I21,Raw_Data_MR!K21)</f>
+        <v/>
+      </c>
+      <c r="L21" s="17">
+        <f>MEDIAN(Raw_Data_MR!G21,Raw_Data_MR!H21,Raw_Data_MR!I21,Raw_Data_MR!J21)</f>
+        <v/>
+      </c>
+      <c r="M21" s="31">
+        <f>Raw_Data_MR!C21/MAX(D21,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N21" s="31">
+        <f>Raw_Data_MR!D21/MAX(E21,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O21" s="31">
+        <f>Raw_Data_MR!E21/MAX(F21,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P21" s="31">
+        <f>Raw_Data_MR!F21/MAX(G21,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="31">
+        <f>Raw_Data_MR!G21/MAX(H21,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R21" s="31">
+        <f>Raw_Data_MR!H21/MAX(I21,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S21" s="31">
+        <f>Raw_Data_MR!I21/MAX(J21,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T21" s="31">
+        <f>Raw_Data_MR!J21/MAX(K21,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U21" s="31">
+        <f>Raw_Data_MR!K21/MAX(L21,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V21" s="5">
+        <f>IF(AND(M21&lt;cfg_mr_ratio_threshold,$C21=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W21" s="5">
+        <f>IF(AND(N21&lt;cfg_mr_ratio_threshold,$C21=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X21" s="5">
+        <f>IF(AND(O21&lt;cfg_mr_ratio_threshold,$C21=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y21" s="5">
+        <f>IF(AND(P21&lt;cfg_mr_ratio_threshold,$C21=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z21" s="5">
+        <f>IF(AND(Q21&lt;cfg_mr_ratio_threshold,$C21=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA21" s="5">
+        <f>IF(AND(R21&lt;cfg_mr_ratio_threshold,$C21=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB21" s="5">
+        <f>IF(AND(S21&lt;cfg_mr_ratio_threshold,$C21=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC21" s="5">
+        <f>IF(AND(T21&lt;cfg_mr_ratio_threshold,$C21=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD21" s="5">
+        <f>IF(AND(U21&lt;cfg_mr_ratio_threshold,$C21=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE21" s="5">
+        <f>IF(V21=1,AE20+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF21" s="5">
+        <f>IF(W21=1,AF20+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG21" s="5">
+        <f>IF(X21=1,AG20+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH21" s="5">
+        <f>IF(Y21=1,AH20+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI21" s="5">
+        <f>IF(Z21=1,AI20+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ21" s="5">
+        <f>IF(AA21=1,AJ20+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK21" s="5">
+        <f>IF(AB21=1,AK20+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL21" s="5">
+        <f>IF(AC21=1,AL20+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM21" s="5">
+        <f>IF(AD21=1,AM20+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="40">
+        <f>Raw_Data_MR!A22</f>
+        <v/>
+      </c>
+      <c r="B22" s="5">
+        <f>Raw_Data_MR!B22</f>
+        <v/>
+      </c>
+      <c r="C22" s="5">
+        <f>IF(AND(B22&gt;cfg_mr_poa_threshold_wm2,B22&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D22" s="17">
+        <f>MEDIAN(Raw_Data_MR!D22,Raw_Data_MR!E22,Raw_Data_MR!F22)</f>
+        <v/>
+      </c>
+      <c r="E22" s="17">
+        <f>MEDIAN(Raw_Data_MR!C22,Raw_Data_MR!E22,Raw_Data_MR!F22)</f>
+        <v/>
+      </c>
+      <c r="F22" s="17">
+        <f>MEDIAN(Raw_Data_MR!C22,Raw_Data_MR!D22,Raw_Data_MR!F22)</f>
+        <v/>
+      </c>
+      <c r="G22" s="17">
+        <f>MEDIAN(Raw_Data_MR!C22,Raw_Data_MR!D22,Raw_Data_MR!E22)</f>
+        <v/>
+      </c>
+      <c r="H22" s="17">
+        <f>MEDIAN(Raw_Data_MR!H22,Raw_Data_MR!I22,Raw_Data_MR!J22,Raw_Data_MR!K22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="17">
+        <f>MEDIAN(Raw_Data_MR!G22,Raw_Data_MR!I22,Raw_Data_MR!J22,Raw_Data_MR!K22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="17">
+        <f>MEDIAN(Raw_Data_MR!G22,Raw_Data_MR!H22,Raw_Data_MR!J22,Raw_Data_MR!K22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="17">
+        <f>MEDIAN(Raw_Data_MR!G22,Raw_Data_MR!H22,Raw_Data_MR!I22,Raw_Data_MR!K22)</f>
+        <v/>
+      </c>
+      <c r="L22" s="17">
+        <f>MEDIAN(Raw_Data_MR!G22,Raw_Data_MR!H22,Raw_Data_MR!I22,Raw_Data_MR!J22)</f>
+        <v/>
+      </c>
+      <c r="M22" s="31">
+        <f>Raw_Data_MR!C22/MAX(D22,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N22" s="31">
+        <f>Raw_Data_MR!D22/MAX(E22,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O22" s="31">
+        <f>Raw_Data_MR!E22/MAX(F22,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P22" s="31">
+        <f>Raw_Data_MR!F22/MAX(G22,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q22" s="31">
+        <f>Raw_Data_MR!G22/MAX(H22,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R22" s="31">
+        <f>Raw_Data_MR!H22/MAX(I22,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S22" s="31">
+        <f>Raw_Data_MR!I22/MAX(J22,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T22" s="31">
+        <f>Raw_Data_MR!J22/MAX(K22,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U22" s="31">
+        <f>Raw_Data_MR!K22/MAX(L22,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V22" s="5">
+        <f>IF(AND(M22&lt;cfg_mr_ratio_threshold,$C22=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W22" s="5">
+        <f>IF(AND(N22&lt;cfg_mr_ratio_threshold,$C22=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X22" s="5">
+        <f>IF(AND(O22&lt;cfg_mr_ratio_threshold,$C22=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y22" s="5">
+        <f>IF(AND(P22&lt;cfg_mr_ratio_threshold,$C22=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z22" s="5">
+        <f>IF(AND(Q22&lt;cfg_mr_ratio_threshold,$C22=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA22" s="5">
+        <f>IF(AND(R22&lt;cfg_mr_ratio_threshold,$C22=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB22" s="5">
+        <f>IF(AND(S22&lt;cfg_mr_ratio_threshold,$C22=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC22" s="5">
+        <f>IF(AND(T22&lt;cfg_mr_ratio_threshold,$C22=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD22" s="5">
+        <f>IF(AND(U22&lt;cfg_mr_ratio_threshold,$C22=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE22" s="5">
+        <f>IF(V22=1,AE21+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF22" s="5">
+        <f>IF(W22=1,AF21+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG22" s="5">
+        <f>IF(X22=1,AG21+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH22" s="5">
+        <f>IF(Y22=1,AH21+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI22" s="5">
+        <f>IF(Z22=1,AI21+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ22" s="5">
+        <f>IF(AA22=1,AJ21+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK22" s="5">
+        <f>IF(AB22=1,AK21+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL22" s="5">
+        <f>IF(AC22=1,AL21+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM22" s="5">
+        <f>IF(AD22=1,AM21+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="40">
+        <f>Raw_Data_MR!A23</f>
+        <v/>
+      </c>
+      <c r="B23" s="5">
+        <f>Raw_Data_MR!B23</f>
+        <v/>
+      </c>
+      <c r="C23" s="5">
+        <f>IF(AND(B23&gt;cfg_mr_poa_threshold_wm2,B23&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D23" s="17">
+        <f>MEDIAN(Raw_Data_MR!D23,Raw_Data_MR!E23,Raw_Data_MR!F23)</f>
+        <v/>
+      </c>
+      <c r="E23" s="17">
+        <f>MEDIAN(Raw_Data_MR!C23,Raw_Data_MR!E23,Raw_Data_MR!F23)</f>
+        <v/>
+      </c>
+      <c r="F23" s="17">
+        <f>MEDIAN(Raw_Data_MR!C23,Raw_Data_MR!D23,Raw_Data_MR!F23)</f>
+        <v/>
+      </c>
+      <c r="G23" s="17">
+        <f>MEDIAN(Raw_Data_MR!C23,Raw_Data_MR!D23,Raw_Data_MR!E23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="17">
+        <f>MEDIAN(Raw_Data_MR!H23,Raw_Data_MR!I23,Raw_Data_MR!J23,Raw_Data_MR!K23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="17">
+        <f>MEDIAN(Raw_Data_MR!G23,Raw_Data_MR!I23,Raw_Data_MR!J23,Raw_Data_MR!K23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="17">
+        <f>MEDIAN(Raw_Data_MR!G23,Raw_Data_MR!H23,Raw_Data_MR!J23,Raw_Data_MR!K23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="17">
+        <f>MEDIAN(Raw_Data_MR!G23,Raw_Data_MR!H23,Raw_Data_MR!I23,Raw_Data_MR!K23)</f>
+        <v/>
+      </c>
+      <c r="L23" s="17">
+        <f>MEDIAN(Raw_Data_MR!G23,Raw_Data_MR!H23,Raw_Data_MR!I23,Raw_Data_MR!J23)</f>
+        <v/>
+      </c>
+      <c r="M23" s="31">
+        <f>Raw_Data_MR!C23/MAX(D23,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N23" s="31">
+        <f>Raw_Data_MR!D23/MAX(E23,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O23" s="31">
+        <f>Raw_Data_MR!E23/MAX(F23,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P23" s="31">
+        <f>Raw_Data_MR!F23/MAX(G23,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q23" s="31">
+        <f>Raw_Data_MR!G23/MAX(H23,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R23" s="31">
+        <f>Raw_Data_MR!H23/MAX(I23,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S23" s="31">
+        <f>Raw_Data_MR!I23/MAX(J23,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T23" s="31">
+        <f>Raw_Data_MR!J23/MAX(K23,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U23" s="31">
+        <f>Raw_Data_MR!K23/MAX(L23,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V23" s="5">
+        <f>IF(AND(M23&lt;cfg_mr_ratio_threshold,$C23=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W23" s="5">
+        <f>IF(AND(N23&lt;cfg_mr_ratio_threshold,$C23=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X23" s="5">
+        <f>IF(AND(O23&lt;cfg_mr_ratio_threshold,$C23=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y23" s="5">
+        <f>IF(AND(P23&lt;cfg_mr_ratio_threshold,$C23=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z23" s="5">
+        <f>IF(AND(Q23&lt;cfg_mr_ratio_threshold,$C23=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA23" s="5">
+        <f>IF(AND(R23&lt;cfg_mr_ratio_threshold,$C23=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB23" s="5">
+        <f>IF(AND(S23&lt;cfg_mr_ratio_threshold,$C23=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC23" s="5">
+        <f>IF(AND(T23&lt;cfg_mr_ratio_threshold,$C23=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD23" s="5">
+        <f>IF(AND(U23&lt;cfg_mr_ratio_threshold,$C23=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE23" s="5">
+        <f>IF(V23=1,AE22+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF23" s="5">
+        <f>IF(W23=1,AF22+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG23" s="5">
+        <f>IF(X23=1,AG22+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH23" s="5">
+        <f>IF(Y23=1,AH22+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI23" s="5">
+        <f>IF(Z23=1,AI22+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ23" s="5">
+        <f>IF(AA23=1,AJ22+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK23" s="5">
+        <f>IF(AB23=1,AK22+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL23" s="5">
+        <f>IF(AC23=1,AL22+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM23" s="5">
+        <f>IF(AD23=1,AM22+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="40">
+        <f>Raw_Data_MR!A24</f>
+        <v/>
+      </c>
+      <c r="B24" s="5">
+        <f>Raw_Data_MR!B24</f>
+        <v/>
+      </c>
+      <c r="C24" s="5">
+        <f>IF(AND(B24&gt;cfg_mr_poa_threshold_wm2,B24&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D24" s="17">
+        <f>MEDIAN(Raw_Data_MR!D24,Raw_Data_MR!E24,Raw_Data_MR!F24)</f>
+        <v/>
+      </c>
+      <c r="E24" s="17">
+        <f>MEDIAN(Raw_Data_MR!C24,Raw_Data_MR!E24,Raw_Data_MR!F24)</f>
+        <v/>
+      </c>
+      <c r="F24" s="17">
+        <f>MEDIAN(Raw_Data_MR!C24,Raw_Data_MR!D24,Raw_Data_MR!F24)</f>
+        <v/>
+      </c>
+      <c r="G24" s="17">
+        <f>MEDIAN(Raw_Data_MR!C24,Raw_Data_MR!D24,Raw_Data_MR!E24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="17">
+        <f>MEDIAN(Raw_Data_MR!H24,Raw_Data_MR!I24,Raw_Data_MR!J24,Raw_Data_MR!K24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="17">
+        <f>MEDIAN(Raw_Data_MR!G24,Raw_Data_MR!I24,Raw_Data_MR!J24,Raw_Data_MR!K24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="17">
+        <f>MEDIAN(Raw_Data_MR!G24,Raw_Data_MR!H24,Raw_Data_MR!J24,Raw_Data_MR!K24)</f>
+        <v/>
+      </c>
+      <c r="K24" s="17">
+        <f>MEDIAN(Raw_Data_MR!G24,Raw_Data_MR!H24,Raw_Data_MR!I24,Raw_Data_MR!K24)</f>
+        <v/>
+      </c>
+      <c r="L24" s="17">
+        <f>MEDIAN(Raw_Data_MR!G24,Raw_Data_MR!H24,Raw_Data_MR!I24,Raw_Data_MR!J24)</f>
+        <v/>
+      </c>
+      <c r="M24" s="31">
+        <f>Raw_Data_MR!C24/MAX(D24,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N24" s="31">
+        <f>Raw_Data_MR!D24/MAX(E24,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O24" s="31">
+        <f>Raw_Data_MR!E24/MAX(F24,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P24" s="31">
+        <f>Raw_Data_MR!F24/MAX(G24,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q24" s="31">
+        <f>Raw_Data_MR!G24/MAX(H24,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R24" s="31">
+        <f>Raw_Data_MR!H24/MAX(I24,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S24" s="31">
+        <f>Raw_Data_MR!I24/MAX(J24,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T24" s="31">
+        <f>Raw_Data_MR!J24/MAX(K24,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U24" s="31">
+        <f>Raw_Data_MR!K24/MAX(L24,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V24" s="5">
+        <f>IF(AND(M24&lt;cfg_mr_ratio_threshold,$C24=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W24" s="5">
+        <f>IF(AND(N24&lt;cfg_mr_ratio_threshold,$C24=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X24" s="5">
+        <f>IF(AND(O24&lt;cfg_mr_ratio_threshold,$C24=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y24" s="5">
+        <f>IF(AND(P24&lt;cfg_mr_ratio_threshold,$C24=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z24" s="5">
+        <f>IF(AND(Q24&lt;cfg_mr_ratio_threshold,$C24=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA24" s="5">
+        <f>IF(AND(R24&lt;cfg_mr_ratio_threshold,$C24=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB24" s="5">
+        <f>IF(AND(S24&lt;cfg_mr_ratio_threshold,$C24=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC24" s="5">
+        <f>IF(AND(T24&lt;cfg_mr_ratio_threshold,$C24=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD24" s="5">
+        <f>IF(AND(U24&lt;cfg_mr_ratio_threshold,$C24=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE24" s="5">
+        <f>IF(V24=1,AE23+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF24" s="5">
+        <f>IF(W24=1,AF23+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG24" s="5">
+        <f>IF(X24=1,AG23+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH24" s="5">
+        <f>IF(Y24=1,AH23+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI24" s="5">
+        <f>IF(Z24=1,AI23+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ24" s="5">
+        <f>IF(AA24=1,AJ23+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK24" s="5">
+        <f>IF(AB24=1,AK23+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL24" s="5">
+        <f>IF(AC24=1,AL23+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM24" s="5">
+        <f>IF(AD24=1,AM23+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="40">
+        <f>Raw_Data_MR!A25</f>
+        <v/>
+      </c>
+      <c r="B25" s="5">
+        <f>Raw_Data_MR!B25</f>
+        <v/>
+      </c>
+      <c r="C25" s="5">
+        <f>IF(AND(B25&gt;cfg_mr_poa_threshold_wm2,B25&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D25" s="17">
+        <f>MEDIAN(Raw_Data_MR!D25,Raw_Data_MR!E25,Raw_Data_MR!F25)</f>
+        <v/>
+      </c>
+      <c r="E25" s="17">
+        <f>MEDIAN(Raw_Data_MR!C25,Raw_Data_MR!E25,Raw_Data_MR!F25)</f>
+        <v/>
+      </c>
+      <c r="F25" s="17">
+        <f>MEDIAN(Raw_Data_MR!C25,Raw_Data_MR!D25,Raw_Data_MR!F25)</f>
+        <v/>
+      </c>
+      <c r="G25" s="17">
+        <f>MEDIAN(Raw_Data_MR!C25,Raw_Data_MR!D25,Raw_Data_MR!E25)</f>
+        <v/>
+      </c>
+      <c r="H25" s="17">
+        <f>MEDIAN(Raw_Data_MR!H25,Raw_Data_MR!I25,Raw_Data_MR!J25,Raw_Data_MR!K25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="17">
+        <f>MEDIAN(Raw_Data_MR!G25,Raw_Data_MR!I25,Raw_Data_MR!J25,Raw_Data_MR!K25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="17">
+        <f>MEDIAN(Raw_Data_MR!G25,Raw_Data_MR!H25,Raw_Data_MR!J25,Raw_Data_MR!K25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="17">
+        <f>MEDIAN(Raw_Data_MR!G25,Raw_Data_MR!H25,Raw_Data_MR!I25,Raw_Data_MR!K25)</f>
+        <v/>
+      </c>
+      <c r="L25" s="17">
+        <f>MEDIAN(Raw_Data_MR!G25,Raw_Data_MR!H25,Raw_Data_MR!I25,Raw_Data_MR!J25)</f>
+        <v/>
+      </c>
+      <c r="M25" s="31">
+        <f>Raw_Data_MR!C25/MAX(D25,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N25" s="31">
+        <f>Raw_Data_MR!D25/MAX(E25,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O25" s="31">
+        <f>Raw_Data_MR!E25/MAX(F25,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P25" s="31">
+        <f>Raw_Data_MR!F25/MAX(G25,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="31">
+        <f>Raw_Data_MR!G25/MAX(H25,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R25" s="31">
+        <f>Raw_Data_MR!H25/MAX(I25,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S25" s="31">
+        <f>Raw_Data_MR!I25/MAX(J25,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T25" s="31">
+        <f>Raw_Data_MR!J25/MAX(K25,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U25" s="31">
+        <f>Raw_Data_MR!K25/MAX(L25,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V25" s="5">
+        <f>IF(AND(M25&lt;cfg_mr_ratio_threshold,$C25=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W25" s="5">
+        <f>IF(AND(N25&lt;cfg_mr_ratio_threshold,$C25=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X25" s="5">
+        <f>IF(AND(O25&lt;cfg_mr_ratio_threshold,$C25=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y25" s="5">
+        <f>IF(AND(P25&lt;cfg_mr_ratio_threshold,$C25=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z25" s="5">
+        <f>IF(AND(Q25&lt;cfg_mr_ratio_threshold,$C25=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA25" s="5">
+        <f>IF(AND(R25&lt;cfg_mr_ratio_threshold,$C25=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB25" s="5">
+        <f>IF(AND(S25&lt;cfg_mr_ratio_threshold,$C25=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC25" s="5">
+        <f>IF(AND(T25&lt;cfg_mr_ratio_threshold,$C25=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD25" s="5">
+        <f>IF(AND(U25&lt;cfg_mr_ratio_threshold,$C25=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE25" s="5">
+        <f>IF(V25=1,AE24+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF25" s="5">
+        <f>IF(W25=1,AF24+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG25" s="5">
+        <f>IF(X25=1,AG24+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH25" s="5">
+        <f>IF(Y25=1,AH24+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI25" s="5">
+        <f>IF(Z25=1,AI24+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ25" s="5">
+        <f>IF(AA25=1,AJ24+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK25" s="5">
+        <f>IF(AB25=1,AK24+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL25" s="5">
+        <f>IF(AC25=1,AL24+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM25" s="5">
+        <f>IF(AD25=1,AM24+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="40">
+        <f>Raw_Data_MR!A26</f>
+        <v/>
+      </c>
+      <c r="B26" s="5">
+        <f>Raw_Data_MR!B26</f>
+        <v/>
+      </c>
+      <c r="C26" s="5">
+        <f>IF(AND(B26&gt;cfg_mr_poa_threshold_wm2,B26&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D26" s="17">
+        <f>MEDIAN(Raw_Data_MR!D26,Raw_Data_MR!E26,Raw_Data_MR!F26)</f>
+        <v/>
+      </c>
+      <c r="E26" s="17">
+        <f>MEDIAN(Raw_Data_MR!C26,Raw_Data_MR!E26,Raw_Data_MR!F26)</f>
+        <v/>
+      </c>
+      <c r="F26" s="17">
+        <f>MEDIAN(Raw_Data_MR!C26,Raw_Data_MR!D26,Raw_Data_MR!F26)</f>
+        <v/>
+      </c>
+      <c r="G26" s="17">
+        <f>MEDIAN(Raw_Data_MR!C26,Raw_Data_MR!D26,Raw_Data_MR!E26)</f>
+        <v/>
+      </c>
+      <c r="H26" s="17">
+        <f>MEDIAN(Raw_Data_MR!H26,Raw_Data_MR!I26,Raw_Data_MR!J26,Raw_Data_MR!K26)</f>
+        <v/>
+      </c>
+      <c r="I26" s="17">
+        <f>MEDIAN(Raw_Data_MR!G26,Raw_Data_MR!I26,Raw_Data_MR!J26,Raw_Data_MR!K26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="17">
+        <f>MEDIAN(Raw_Data_MR!G26,Raw_Data_MR!H26,Raw_Data_MR!J26,Raw_Data_MR!K26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="17">
+        <f>MEDIAN(Raw_Data_MR!G26,Raw_Data_MR!H26,Raw_Data_MR!I26,Raw_Data_MR!K26)</f>
+        <v/>
+      </c>
+      <c r="L26" s="17">
+        <f>MEDIAN(Raw_Data_MR!G26,Raw_Data_MR!H26,Raw_Data_MR!I26,Raw_Data_MR!J26)</f>
+        <v/>
+      </c>
+      <c r="M26" s="31">
+        <f>Raw_Data_MR!C26/MAX(D26,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N26" s="31">
+        <f>Raw_Data_MR!D26/MAX(E26,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O26" s="31">
+        <f>Raw_Data_MR!E26/MAX(F26,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P26" s="31">
+        <f>Raw_Data_MR!F26/MAX(G26,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q26" s="31">
+        <f>Raw_Data_MR!G26/MAX(H26,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R26" s="31">
+        <f>Raw_Data_MR!H26/MAX(I26,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S26" s="31">
+        <f>Raw_Data_MR!I26/MAX(J26,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T26" s="31">
+        <f>Raw_Data_MR!J26/MAX(K26,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U26" s="31">
+        <f>Raw_Data_MR!K26/MAX(L26,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V26" s="5">
+        <f>IF(AND(M26&lt;cfg_mr_ratio_threshold,$C26=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W26" s="5">
+        <f>IF(AND(N26&lt;cfg_mr_ratio_threshold,$C26=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X26" s="5">
+        <f>IF(AND(O26&lt;cfg_mr_ratio_threshold,$C26=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y26" s="5">
+        <f>IF(AND(P26&lt;cfg_mr_ratio_threshold,$C26=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z26" s="5">
+        <f>IF(AND(Q26&lt;cfg_mr_ratio_threshold,$C26=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA26" s="5">
+        <f>IF(AND(R26&lt;cfg_mr_ratio_threshold,$C26=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB26" s="5">
+        <f>IF(AND(S26&lt;cfg_mr_ratio_threshold,$C26=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC26" s="5">
+        <f>IF(AND(T26&lt;cfg_mr_ratio_threshold,$C26=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD26" s="5">
+        <f>IF(AND(U26&lt;cfg_mr_ratio_threshold,$C26=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE26" s="5">
+        <f>IF(V26=1,AE25+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF26" s="5">
+        <f>IF(W26=1,AF25+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG26" s="5">
+        <f>IF(X26=1,AG25+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH26" s="5">
+        <f>IF(Y26=1,AH25+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI26" s="5">
+        <f>IF(Z26=1,AI25+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ26" s="5">
+        <f>IF(AA26=1,AJ25+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK26" s="5">
+        <f>IF(AB26=1,AK25+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL26" s="5">
+        <f>IF(AC26=1,AL25+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM26" s="5">
+        <f>IF(AD26=1,AM25+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="40">
+        <f>Raw_Data_MR!A27</f>
+        <v/>
+      </c>
+      <c r="B27" s="5">
+        <f>Raw_Data_MR!B27</f>
+        <v/>
+      </c>
+      <c r="C27" s="5">
+        <f>IF(AND(B27&gt;cfg_mr_poa_threshold_wm2,B27&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D27" s="17">
+        <f>MEDIAN(Raw_Data_MR!D27,Raw_Data_MR!E27,Raw_Data_MR!F27)</f>
+        <v/>
+      </c>
+      <c r="E27" s="17">
+        <f>MEDIAN(Raw_Data_MR!C27,Raw_Data_MR!E27,Raw_Data_MR!F27)</f>
+        <v/>
+      </c>
+      <c r="F27" s="17">
+        <f>MEDIAN(Raw_Data_MR!C27,Raw_Data_MR!D27,Raw_Data_MR!F27)</f>
+        <v/>
+      </c>
+      <c r="G27" s="17">
+        <f>MEDIAN(Raw_Data_MR!C27,Raw_Data_MR!D27,Raw_Data_MR!E27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="17">
+        <f>MEDIAN(Raw_Data_MR!H27,Raw_Data_MR!I27,Raw_Data_MR!J27,Raw_Data_MR!K27)</f>
+        <v/>
+      </c>
+      <c r="I27" s="17">
+        <f>MEDIAN(Raw_Data_MR!G27,Raw_Data_MR!I27,Raw_Data_MR!J27,Raw_Data_MR!K27)</f>
+        <v/>
+      </c>
+      <c r="J27" s="17">
+        <f>MEDIAN(Raw_Data_MR!G27,Raw_Data_MR!H27,Raw_Data_MR!J27,Raw_Data_MR!K27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="17">
+        <f>MEDIAN(Raw_Data_MR!G27,Raw_Data_MR!H27,Raw_Data_MR!I27,Raw_Data_MR!K27)</f>
+        <v/>
+      </c>
+      <c r="L27" s="17">
+        <f>MEDIAN(Raw_Data_MR!G27,Raw_Data_MR!H27,Raw_Data_MR!I27,Raw_Data_MR!J27)</f>
+        <v/>
+      </c>
+      <c r="M27" s="31">
+        <f>Raw_Data_MR!C27/MAX(D27,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N27" s="31">
+        <f>Raw_Data_MR!D27/MAX(E27,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O27" s="31">
+        <f>Raw_Data_MR!E27/MAX(F27,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P27" s="31">
+        <f>Raw_Data_MR!F27/MAX(G27,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q27" s="31">
+        <f>Raw_Data_MR!G27/MAX(H27,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R27" s="31">
+        <f>Raw_Data_MR!H27/MAX(I27,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S27" s="31">
+        <f>Raw_Data_MR!I27/MAX(J27,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T27" s="31">
+        <f>Raw_Data_MR!J27/MAX(K27,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U27" s="31">
+        <f>Raw_Data_MR!K27/MAX(L27,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V27" s="5">
+        <f>IF(AND(M27&lt;cfg_mr_ratio_threshold,$C27=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W27" s="5">
+        <f>IF(AND(N27&lt;cfg_mr_ratio_threshold,$C27=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X27" s="5">
+        <f>IF(AND(O27&lt;cfg_mr_ratio_threshold,$C27=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y27" s="5">
+        <f>IF(AND(P27&lt;cfg_mr_ratio_threshold,$C27=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z27" s="5">
+        <f>IF(AND(Q27&lt;cfg_mr_ratio_threshold,$C27=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA27" s="5">
+        <f>IF(AND(R27&lt;cfg_mr_ratio_threshold,$C27=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB27" s="5">
+        <f>IF(AND(S27&lt;cfg_mr_ratio_threshold,$C27=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC27" s="5">
+        <f>IF(AND(T27&lt;cfg_mr_ratio_threshold,$C27=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD27" s="5">
+        <f>IF(AND(U27&lt;cfg_mr_ratio_threshold,$C27=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE27" s="5">
+        <f>IF(V27=1,AE26+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF27" s="5">
+        <f>IF(W27=1,AF26+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG27" s="5">
+        <f>IF(X27=1,AG26+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH27" s="5">
+        <f>IF(Y27=1,AH26+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI27" s="5">
+        <f>IF(Z27=1,AI26+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ27" s="5">
+        <f>IF(AA27=1,AJ26+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK27" s="5">
+        <f>IF(AB27=1,AK26+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL27" s="5">
+        <f>IF(AC27=1,AL26+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM27" s="5">
+        <f>IF(AD27=1,AM26+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="40">
+        <f>Raw_Data_MR!A28</f>
+        <v/>
+      </c>
+      <c r="B28" s="5">
+        <f>Raw_Data_MR!B28</f>
+        <v/>
+      </c>
+      <c r="C28" s="5">
+        <f>IF(AND(B28&gt;cfg_mr_poa_threshold_wm2,B28&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D28" s="17">
+        <f>MEDIAN(Raw_Data_MR!D28,Raw_Data_MR!E28,Raw_Data_MR!F28)</f>
+        <v/>
+      </c>
+      <c r="E28" s="17">
+        <f>MEDIAN(Raw_Data_MR!C28,Raw_Data_MR!E28,Raw_Data_MR!F28)</f>
+        <v/>
+      </c>
+      <c r="F28" s="17">
+        <f>MEDIAN(Raw_Data_MR!C28,Raw_Data_MR!D28,Raw_Data_MR!F28)</f>
+        <v/>
+      </c>
+      <c r="G28" s="17">
+        <f>MEDIAN(Raw_Data_MR!C28,Raw_Data_MR!D28,Raw_Data_MR!E28)</f>
+        <v/>
+      </c>
+      <c r="H28" s="17">
+        <f>MEDIAN(Raw_Data_MR!H28,Raw_Data_MR!I28,Raw_Data_MR!J28,Raw_Data_MR!K28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="17">
+        <f>MEDIAN(Raw_Data_MR!G28,Raw_Data_MR!I28,Raw_Data_MR!J28,Raw_Data_MR!K28)</f>
+        <v/>
+      </c>
+      <c r="J28" s="17">
+        <f>MEDIAN(Raw_Data_MR!G28,Raw_Data_MR!H28,Raw_Data_MR!J28,Raw_Data_MR!K28)</f>
+        <v/>
+      </c>
+      <c r="K28" s="17">
+        <f>MEDIAN(Raw_Data_MR!G28,Raw_Data_MR!H28,Raw_Data_MR!I28,Raw_Data_MR!K28)</f>
+        <v/>
+      </c>
+      <c r="L28" s="17">
+        <f>MEDIAN(Raw_Data_MR!G28,Raw_Data_MR!H28,Raw_Data_MR!I28,Raw_Data_MR!J28)</f>
+        <v/>
+      </c>
+      <c r="M28" s="31">
+        <f>Raw_Data_MR!C28/MAX(D28,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N28" s="31">
+        <f>Raw_Data_MR!D28/MAX(E28,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O28" s="31">
+        <f>Raw_Data_MR!E28/MAX(F28,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P28" s="31">
+        <f>Raw_Data_MR!F28/MAX(G28,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q28" s="31">
+        <f>Raw_Data_MR!G28/MAX(H28,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R28" s="31">
+        <f>Raw_Data_MR!H28/MAX(I28,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S28" s="31">
+        <f>Raw_Data_MR!I28/MAX(J28,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T28" s="31">
+        <f>Raw_Data_MR!J28/MAX(K28,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U28" s="31">
+        <f>Raw_Data_MR!K28/MAX(L28,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V28" s="5">
+        <f>IF(AND(M28&lt;cfg_mr_ratio_threshold,$C28=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W28" s="5">
+        <f>IF(AND(N28&lt;cfg_mr_ratio_threshold,$C28=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X28" s="5">
+        <f>IF(AND(O28&lt;cfg_mr_ratio_threshold,$C28=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y28" s="5">
+        <f>IF(AND(P28&lt;cfg_mr_ratio_threshold,$C28=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z28" s="5">
+        <f>IF(AND(Q28&lt;cfg_mr_ratio_threshold,$C28=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA28" s="5">
+        <f>IF(AND(R28&lt;cfg_mr_ratio_threshold,$C28=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB28" s="5">
+        <f>IF(AND(S28&lt;cfg_mr_ratio_threshold,$C28=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC28" s="5">
+        <f>IF(AND(T28&lt;cfg_mr_ratio_threshold,$C28=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD28" s="5">
+        <f>IF(AND(U28&lt;cfg_mr_ratio_threshold,$C28=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE28" s="5">
+        <f>IF(V28=1,AE27+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF28" s="5">
+        <f>IF(W28=1,AF27+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG28" s="5">
+        <f>IF(X28=1,AG27+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH28" s="5">
+        <f>IF(Y28=1,AH27+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI28" s="5">
+        <f>IF(Z28=1,AI27+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ28" s="5">
+        <f>IF(AA28=1,AJ27+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK28" s="5">
+        <f>IF(AB28=1,AK27+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL28" s="5">
+        <f>IF(AC28=1,AL27+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM28" s="5">
+        <f>IF(AD28=1,AM27+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="40">
+        <f>Raw_Data_MR!A29</f>
+        <v/>
+      </c>
+      <c r="B29" s="5">
+        <f>Raw_Data_MR!B29</f>
+        <v/>
+      </c>
+      <c r="C29" s="5">
+        <f>IF(AND(B29&gt;cfg_mr_poa_threshold_wm2,B29&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D29" s="17">
+        <f>MEDIAN(Raw_Data_MR!D29,Raw_Data_MR!E29,Raw_Data_MR!F29)</f>
+        <v/>
+      </c>
+      <c r="E29" s="17">
+        <f>MEDIAN(Raw_Data_MR!C29,Raw_Data_MR!E29,Raw_Data_MR!F29)</f>
+        <v/>
+      </c>
+      <c r="F29" s="17">
+        <f>MEDIAN(Raw_Data_MR!C29,Raw_Data_MR!D29,Raw_Data_MR!F29)</f>
+        <v/>
+      </c>
+      <c r="G29" s="17">
+        <f>MEDIAN(Raw_Data_MR!C29,Raw_Data_MR!D29,Raw_Data_MR!E29)</f>
+        <v/>
+      </c>
+      <c r="H29" s="17">
+        <f>MEDIAN(Raw_Data_MR!H29,Raw_Data_MR!I29,Raw_Data_MR!J29,Raw_Data_MR!K29)</f>
+        <v/>
+      </c>
+      <c r="I29" s="17">
+        <f>MEDIAN(Raw_Data_MR!G29,Raw_Data_MR!I29,Raw_Data_MR!J29,Raw_Data_MR!K29)</f>
+        <v/>
+      </c>
+      <c r="J29" s="17">
+        <f>MEDIAN(Raw_Data_MR!G29,Raw_Data_MR!H29,Raw_Data_MR!J29,Raw_Data_MR!K29)</f>
+        <v/>
+      </c>
+      <c r="K29" s="17">
+        <f>MEDIAN(Raw_Data_MR!G29,Raw_Data_MR!H29,Raw_Data_MR!I29,Raw_Data_MR!K29)</f>
+        <v/>
+      </c>
+      <c r="L29" s="17">
+        <f>MEDIAN(Raw_Data_MR!G29,Raw_Data_MR!H29,Raw_Data_MR!I29,Raw_Data_MR!J29)</f>
+        <v/>
+      </c>
+      <c r="M29" s="31">
+        <f>Raw_Data_MR!C29/MAX(D29,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N29" s="31">
+        <f>Raw_Data_MR!D29/MAX(E29,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O29" s="31">
+        <f>Raw_Data_MR!E29/MAX(F29,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P29" s="31">
+        <f>Raw_Data_MR!F29/MAX(G29,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q29" s="31">
+        <f>Raw_Data_MR!G29/MAX(H29,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R29" s="31">
+        <f>Raw_Data_MR!H29/MAX(I29,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S29" s="31">
+        <f>Raw_Data_MR!I29/MAX(J29,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T29" s="31">
+        <f>Raw_Data_MR!J29/MAX(K29,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U29" s="31">
+        <f>Raw_Data_MR!K29/MAX(L29,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V29" s="5">
+        <f>IF(AND(M29&lt;cfg_mr_ratio_threshold,$C29=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W29" s="5">
+        <f>IF(AND(N29&lt;cfg_mr_ratio_threshold,$C29=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X29" s="5">
+        <f>IF(AND(O29&lt;cfg_mr_ratio_threshold,$C29=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y29" s="5">
+        <f>IF(AND(P29&lt;cfg_mr_ratio_threshold,$C29=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z29" s="5">
+        <f>IF(AND(Q29&lt;cfg_mr_ratio_threshold,$C29=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA29" s="5">
+        <f>IF(AND(R29&lt;cfg_mr_ratio_threshold,$C29=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB29" s="5">
+        <f>IF(AND(S29&lt;cfg_mr_ratio_threshold,$C29=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC29" s="5">
+        <f>IF(AND(T29&lt;cfg_mr_ratio_threshold,$C29=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD29" s="5">
+        <f>IF(AND(U29&lt;cfg_mr_ratio_threshold,$C29=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE29" s="5">
+        <f>IF(V29=1,AE28+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF29" s="5">
+        <f>IF(W29=1,AF28+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG29" s="5">
+        <f>IF(X29=1,AG28+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH29" s="5">
+        <f>IF(Y29=1,AH28+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI29" s="5">
+        <f>IF(Z29=1,AI28+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ29" s="5">
+        <f>IF(AA29=1,AJ28+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK29" s="5">
+        <f>IF(AB29=1,AK28+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL29" s="5">
+        <f>IF(AC29=1,AL28+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM29" s="5">
+        <f>IF(AD29=1,AM28+1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="40">
+        <f>Raw_Data_MR!A30</f>
+        <v/>
+      </c>
+      <c r="B30" s="5">
+        <f>Raw_Data_MR!B30</f>
+        <v/>
+      </c>
+      <c r="C30" s="5">
+        <f>IF(AND(B30&gt;cfg_mr_poa_threshold_wm2,B30&gt;cfg_mr_poa_floor_wm2),1,0)</f>
+        <v/>
+      </c>
+      <c r="D30" s="17">
+        <f>MEDIAN(Raw_Data_MR!D30,Raw_Data_MR!E30,Raw_Data_MR!F30)</f>
+        <v/>
+      </c>
+      <c r="E30" s="17">
+        <f>MEDIAN(Raw_Data_MR!C30,Raw_Data_MR!E30,Raw_Data_MR!F30)</f>
+        <v/>
+      </c>
+      <c r="F30" s="17">
+        <f>MEDIAN(Raw_Data_MR!C30,Raw_Data_MR!D30,Raw_Data_MR!F30)</f>
+        <v/>
+      </c>
+      <c r="G30" s="17">
+        <f>MEDIAN(Raw_Data_MR!C30,Raw_Data_MR!D30,Raw_Data_MR!E30)</f>
+        <v/>
+      </c>
+      <c r="H30" s="17">
+        <f>MEDIAN(Raw_Data_MR!H30,Raw_Data_MR!I30,Raw_Data_MR!J30,Raw_Data_MR!K30)</f>
+        <v/>
+      </c>
+      <c r="I30" s="17">
+        <f>MEDIAN(Raw_Data_MR!G30,Raw_Data_MR!I30,Raw_Data_MR!J30,Raw_Data_MR!K30)</f>
+        <v/>
+      </c>
+      <c r="J30" s="17">
+        <f>MEDIAN(Raw_Data_MR!G30,Raw_Data_MR!H30,Raw_Data_MR!J30,Raw_Data_MR!K30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="17">
+        <f>MEDIAN(Raw_Data_MR!G30,Raw_Data_MR!H30,Raw_Data_MR!I30,Raw_Data_MR!K30)</f>
+        <v/>
+      </c>
+      <c r="L30" s="17">
+        <f>MEDIAN(Raw_Data_MR!G30,Raw_Data_MR!H30,Raw_Data_MR!I30,Raw_Data_MR!J30)</f>
+        <v/>
+      </c>
+      <c r="M30" s="31">
+        <f>Raw_Data_MR!C30/MAX(D30,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="N30" s="31">
+        <f>Raw_Data_MR!D30/MAX(E30,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="O30" s="31">
+        <f>Raw_Data_MR!E30/MAX(F30,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="P30" s="31">
+        <f>Raw_Data_MR!F30/MAX(G30,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="Q30" s="31">
+        <f>Raw_Data_MR!G30/MAX(H30,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="R30" s="31">
+        <f>Raw_Data_MR!H30/MAX(I30,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="S30" s="31">
+        <f>Raw_Data_MR!I30/MAX(J30,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="T30" s="31">
+        <f>Raw_Data_MR!J30/MAX(K30,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="U30" s="31">
+        <f>Raw_Data_MR!K30/MAX(L30,cfg_mr_partner_clip)</f>
+        <v/>
+      </c>
+      <c r="V30" s="5">
+        <f>IF(AND(M30&lt;cfg_mr_ratio_threshold,$C30=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="W30" s="5">
+        <f>IF(AND(N30&lt;cfg_mr_ratio_threshold,$C30=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="X30" s="5">
+        <f>IF(AND(O30&lt;cfg_mr_ratio_threshold,$C30=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Y30" s="5">
+        <f>IF(AND(P30&lt;cfg_mr_ratio_threshold,$C30=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="Z30" s="5">
+        <f>IF(AND(Q30&lt;cfg_mr_ratio_threshold,$C30=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AA30" s="5">
+        <f>IF(AND(R30&lt;cfg_mr_ratio_threshold,$C30=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AB30" s="5">
+        <f>IF(AND(S30&lt;cfg_mr_ratio_threshold,$C30=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AC30" s="5">
+        <f>IF(AND(T30&lt;cfg_mr_ratio_threshold,$C30=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AD30" s="5">
+        <f>IF(AND(U30&lt;cfg_mr_ratio_threshold,$C30=1),1,0)</f>
+        <v/>
+      </c>
+      <c r="AE30" s="5">
+        <f>IF(V30=1,AE29+1,0)</f>
+        <v/>
+      </c>
+      <c r="AF30" s="5">
+        <f>IF(W30=1,AF29+1,0)</f>
+        <v/>
+      </c>
+      <c r="AG30" s="5">
+        <f>IF(X30=1,AG29+1,0)</f>
+        <v/>
+      </c>
+      <c r="AH30" s="5">
+        <f>IF(Y30=1,AH29+1,0)</f>
+        <v/>
+      </c>
+      <c r="AI30" s="5">
+        <f>IF(Z30=1,AI29+1,0)</f>
+        <v/>
+      </c>
+      <c r="AJ30" s="5">
+        <f>IF(AA30=1,AJ29+1,0)</f>
+        <v/>
+      </c>
+      <c r="AK30" s="5">
+        <f>IF(AB30=1,AK29+1,0)</f>
+        <v/>
+      </c>
+      <c r="AL30" s="5">
+        <f>IF(AC30=1,AL29+1,0)</f>
+        <v/>
+      </c>
+      <c r="AM30" s="5">
+        <f>IF(AD30=1,AM29+1,0)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>M2b_MpptRatio — keputusan per string (LIVE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>value = ratio_median_daylight ; emit bila max_consec &gt;= cfg_mr_debounce_steps DAN bukan EMPTY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>severity: value&lt;critical CRIT | &lt;high HIGH | else MED. confidence = min(90,max(50,(1-value)*100)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>pv_string</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>mppt</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>partner_strings</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>ratio_median_daylight</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>max_consec</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>empty_by_design</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>emit</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>PV1</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>PV2, PV3, PV4</t>
+        </is>
+      </c>
+      <c r="D5" s="31">
+        <f>MEDIAN(Helpers_MR!M5:M28)</f>
+        <v/>
+      </c>
+      <c r="E5" s="5">
+        <f>MAX(Helpers_MR!AE5:AE30)</f>
+        <v/>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <f>IF(AND(E5&gt;=cfg_mr_debounce_steps,F5=0),1,0)</f>
+        <v/>
+      </c>
+      <c r="H5" s="5">
+        <f>IF(G5=0,"",IF(D5&lt;cfg_mr_ratio_critical,"CRITICAL",IF(D5&lt;cfg_mr_ratio_high,"HIGH","MEDIUM")))</f>
+        <v/>
+      </c>
+      <c r="I5" s="62">
+        <f>IF(G5=0,"",MIN(90,MAX(50,(1-D5)*100)))</f>
+        <v/>
+      </c>
+      <c r="J5" s="5">
+        <f>IF(F5=1,"EMPTY",IF(G5=1,"mppt_partner_underperform","NORMAL"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>PV2</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>PV1, PV3, PV4</t>
+        </is>
+      </c>
+      <c r="D6" s="31">
+        <f>MEDIAN(Helpers_MR!N5:N28)</f>
+        <v/>
+      </c>
+      <c r="E6" s="5">
+        <f>MAX(Helpers_MR!AF5:AF30)</f>
+        <v/>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <f>IF(AND(E6&gt;=cfg_mr_debounce_steps,F6=0),1,0)</f>
+        <v/>
+      </c>
+      <c r="H6" s="5">
+        <f>IF(G6=0,"",IF(D6&lt;cfg_mr_ratio_critical,"CRITICAL",IF(D6&lt;cfg_mr_ratio_high,"HIGH","MEDIUM")))</f>
+        <v/>
+      </c>
+      <c r="I6" s="62">
+        <f>IF(G6=0,"",MIN(90,MAX(50,(1-D6)*100)))</f>
+        <v/>
+      </c>
+      <c r="J6" s="5">
+        <f>IF(F6=1,"EMPTY",IF(G6=1,"mppt_partner_underperform","NORMAL"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>PV3</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>PV1, PV2, PV4</t>
+        </is>
+      </c>
+      <c r="D7" s="31">
+        <f>MEDIAN(Helpers_MR!O5:O28)</f>
+        <v/>
+      </c>
+      <c r="E7" s="5">
+        <f>MAX(Helpers_MR!AG5:AG30)</f>
+        <v/>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <f>IF(AND(E7&gt;=cfg_mr_debounce_steps,F7=0),1,0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="5">
+        <f>IF(G7=0,"",IF(D7&lt;cfg_mr_ratio_critical,"CRITICAL",IF(D7&lt;cfg_mr_ratio_high,"HIGH","MEDIUM")))</f>
+        <v/>
+      </c>
+      <c r="I7" s="62">
+        <f>IF(G7=0,"",MIN(90,MAX(50,(1-D7)*100)))</f>
+        <v/>
+      </c>
+      <c r="J7" s="5">
+        <f>IF(F7=1,"EMPTY",IF(G7=1,"mppt_partner_underperform","NORMAL"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>PV4</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>PV1, PV2, PV3</t>
+        </is>
+      </c>
+      <c r="D8" s="31">
+        <f>MEDIAN(Helpers_MR!P5:P28)</f>
+        <v/>
+      </c>
+      <c r="E8" s="5">
+        <f>MAX(Helpers_MR!AH5:AH30)</f>
+        <v/>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <f>IF(AND(E8&gt;=cfg_mr_debounce_steps,F8=0),1,0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="5">
+        <f>IF(G8=0,"",IF(D8&lt;cfg_mr_ratio_critical,"CRITICAL",IF(D8&lt;cfg_mr_ratio_high,"HIGH","MEDIUM")))</f>
+        <v/>
+      </c>
+      <c r="I8" s="62">
+        <f>IF(G8=0,"",MIN(90,MAX(50,(1-D8)*100)))</f>
+        <v/>
+      </c>
+      <c r="J8" s="5">
+        <f>IF(F8=1,"EMPTY",IF(G8=1,"mppt_partner_underperform","NORMAL"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>PV5</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>PV6, PV7, PV8, PV9</t>
+        </is>
+      </c>
+      <c r="D9" s="31">
+        <f>MEDIAN(Helpers_MR!Q5:Q28)</f>
+        <v/>
+      </c>
+      <c r="E9" s="5">
+        <f>MAX(Helpers_MR!AI5:AI30)</f>
+        <v/>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <f>IF(AND(E9&gt;=cfg_mr_debounce_steps,F9=0),1,0)</f>
+        <v/>
+      </c>
+      <c r="H9" s="5">
+        <f>IF(G9=0,"",IF(D9&lt;cfg_mr_ratio_critical,"CRITICAL",IF(D9&lt;cfg_mr_ratio_high,"HIGH","MEDIUM")))</f>
+        <v/>
+      </c>
+      <c r="I9" s="62">
+        <f>IF(G9=0,"",MIN(90,MAX(50,(1-D9)*100)))</f>
+        <v/>
+      </c>
+      <c r="J9" s="5">
+        <f>IF(F9=1,"EMPTY",IF(G9=1,"mppt_partner_underperform","NORMAL"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>PV6</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>PV5, PV7, PV8, PV9</t>
+        </is>
+      </c>
+      <c r="D10" s="31">
+        <f>MEDIAN(Helpers_MR!R5:R28)</f>
+        <v/>
+      </c>
+      <c r="E10" s="5">
+        <f>MAX(Helpers_MR!AJ5:AJ30)</f>
+        <v/>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <f>IF(AND(E10&gt;=cfg_mr_debounce_steps,F10=0),1,0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="5">
+        <f>IF(G10=0,"",IF(D10&lt;cfg_mr_ratio_critical,"CRITICAL",IF(D10&lt;cfg_mr_ratio_high,"HIGH","MEDIUM")))</f>
+        <v/>
+      </c>
+      <c r="I10" s="62">
+        <f>IF(G10=0,"",MIN(90,MAX(50,(1-D10)*100)))</f>
+        <v/>
+      </c>
+      <c r="J10" s="5">
+        <f>IF(F10=1,"EMPTY",IF(G10=1,"mppt_partner_underperform","NORMAL"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>PV7</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>PV5, PV6, PV8, PV9</t>
+        </is>
+      </c>
+      <c r="D11" s="31">
+        <f>MEDIAN(Helpers_MR!S5:S28)</f>
+        <v/>
+      </c>
+      <c r="E11" s="5">
+        <f>MAX(Helpers_MR!AK5:AK30)</f>
+        <v/>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <f>IF(AND(E11&gt;=cfg_mr_debounce_steps,F11=0),1,0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="5">
+        <f>IF(G11=0,"",IF(D11&lt;cfg_mr_ratio_critical,"CRITICAL",IF(D11&lt;cfg_mr_ratio_high,"HIGH","MEDIUM")))</f>
+        <v/>
+      </c>
+      <c r="I11" s="62">
+        <f>IF(G11=0,"",MIN(90,MAX(50,(1-D11)*100)))</f>
+        <v/>
+      </c>
+      <c r="J11" s="5">
+        <f>IF(F11=1,"EMPTY",IF(G11=1,"mppt_partner_underperform","NORMAL"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>PV8</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>PV5, PV6, PV7, PV9</t>
+        </is>
+      </c>
+      <c r="D12" s="31">
+        <f>MEDIAN(Helpers_MR!T5:T28)</f>
+        <v/>
+      </c>
+      <c r="E12" s="5">
+        <f>MAX(Helpers_MR!AL5:AL30)</f>
+        <v/>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <f>IF(AND(E12&gt;=cfg_mr_debounce_steps,F12=0),1,0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="5">
+        <f>IF(G12=0,"",IF(D12&lt;cfg_mr_ratio_critical,"CRITICAL",IF(D12&lt;cfg_mr_ratio_high,"HIGH","MEDIUM")))</f>
+        <v/>
+      </c>
+      <c r="I12" s="62">
+        <f>IF(G12=0,"",MIN(90,MAX(50,(1-D12)*100)))</f>
+        <v/>
+      </c>
+      <c r="J12" s="5">
+        <f>IF(F12=1,"EMPTY",IF(G12=1,"mppt_partner_underperform","NORMAL"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>PV9</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>PV5, PV6, PV7, PV8</t>
+        </is>
+      </c>
+      <c r="D13" s="31">
+        <f>MEDIAN(Helpers_MR!U5:U28)</f>
+        <v/>
+      </c>
+      <c r="E13" s="5">
+        <f>MAX(Helpers_MR!AM5:AM30)</f>
+        <v/>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <f>IF(AND(E13&gt;=cfg_mr_debounce_steps,F13=0),1,0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="5">
+        <f>IF(G13=0,"",IF(D13&lt;cfg_mr_ratio_critical,"CRITICAL",IF(D13&lt;cfg_mr_ratio_high,"HIGH","MEDIUM")))</f>
+        <v/>
+      </c>
+      <c r="I13" s="62">
+        <f>IF(G13=0,"",MIN(90,MAX(50,(1-D13)*100)))</f>
+        <v/>
+      </c>
+      <c r="J13" s="5">
+        <f>IF(F13=1,"EMPTY",IF(G13=1,"mppt_partner_underperform","NORMAL"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="H5:H13">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"CRITICAL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"HIGH"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="7">
+      <formula>"MEDIUM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="4">
+      <formula>"NORMAL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="8">
+      <formula>"EMPTY"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:J13">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+      <formula>"mppt_partner_underperform"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="4">
+      <formula>"NORMAL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="8">
+      <formula>"EMPTY"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>M2b_MR_StringStatus — replika artifact StringStatus (mppt_ratio.py baris 341-355)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Kolom = field artifact Python. ratio_event_median == ratio_median_daylight untuk fault sustained (M2_RE_11 §5.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>poa_source</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>inverter_id</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>wb_id</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>pv_string</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>mppt</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>partner_strings</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>ratio_median_daylight</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>ratio_event_median</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>n_qualifying_steps</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>n_debounced_events</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>emitted_finding</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>daylight_samples</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>pyranometer_per_ws</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>WB05-INV05</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>WB05</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>PV1</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
+        <f>M2b_MpptRatio!J5</f>
+        <v/>
+      </c>
+      <c r="G5" s="5">
+        <f>M2b_MpptRatio!C5</f>
+        <v/>
+      </c>
+      <c r="H5" s="31">
+        <f>M2b_MpptRatio!D5</f>
+        <v/>
+      </c>
+      <c r="I5" s="31">
+        <f>M2b_MpptRatio!D5</f>
+        <v/>
+      </c>
+      <c r="J5" s="5">
+        <f>SUM(Helpers_MR!V5:V30)</f>
+        <v/>
+      </c>
+      <c r="K5" s="5">
+        <f>M2b_MpptRatio!G5</f>
+        <v/>
+      </c>
+      <c r="L5" s="5">
+        <f>M2b_MpptRatio!G5</f>
+        <v/>
+      </c>
+      <c r="M5" s="5">
+        <f>SUM(Helpers_MR!C5:C30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>pyranometer_per_ws</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>WB05-INV05</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>WB05</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>PV2</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5">
+        <f>M2b_MpptRatio!J6</f>
+        <v/>
+      </c>
+      <c r="G6" s="5">
+        <f>M2b_MpptRatio!C6</f>
+        <v/>
+      </c>
+      <c r="H6" s="31">
+        <f>M2b_MpptRatio!D6</f>
+        <v/>
+      </c>
+      <c r="I6" s="31">
+        <f>M2b_MpptRatio!D6</f>
+        <v/>
+      </c>
+      <c r="J6" s="5">
+        <f>SUM(Helpers_MR!W5:W30)</f>
+        <v/>
+      </c>
+      <c r="K6" s="5">
+        <f>M2b_MpptRatio!G6</f>
+        <v/>
+      </c>
+      <c r="L6" s="5">
+        <f>M2b_MpptRatio!G6</f>
+        <v/>
+      </c>
+      <c r="M6" s="5">
+        <f>SUM(Helpers_MR!C5:C30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>pyranometer_per_ws</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>WB05-INV05</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>WB05</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>PV3</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5">
+        <f>M2b_MpptRatio!J7</f>
+        <v/>
+      </c>
+      <c r="G7" s="5">
+        <f>M2b_MpptRatio!C7</f>
+        <v/>
+      </c>
+      <c r="H7" s="31">
+        <f>M2b_MpptRatio!D7</f>
+        <v/>
+      </c>
+      <c r="I7" s="31">
+        <f>M2b_MpptRatio!D7</f>
+        <v/>
+      </c>
+      <c r="J7" s="5">
+        <f>SUM(Helpers_MR!X5:X30)</f>
+        <v/>
+      </c>
+      <c r="K7" s="5">
+        <f>M2b_MpptRatio!G7</f>
+        <v/>
+      </c>
+      <c r="L7" s="5">
+        <f>M2b_MpptRatio!G7</f>
+        <v/>
+      </c>
+      <c r="M7" s="5">
+        <f>SUM(Helpers_MR!C5:C30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>pyranometer_per_ws</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>WB05-INV05</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>WB05</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>PV4</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
+        <f>M2b_MpptRatio!J8</f>
+        <v/>
+      </c>
+      <c r="G8" s="5">
+        <f>M2b_MpptRatio!C8</f>
+        <v/>
+      </c>
+      <c r="H8" s="31">
+        <f>M2b_MpptRatio!D8</f>
+        <v/>
+      </c>
+      <c r="I8" s="31">
+        <f>M2b_MpptRatio!D8</f>
+        <v/>
+      </c>
+      <c r="J8" s="5">
+        <f>SUM(Helpers_MR!Y5:Y30)</f>
+        <v/>
+      </c>
+      <c r="K8" s="5">
+        <f>M2b_MpptRatio!G8</f>
+        <v/>
+      </c>
+      <c r="L8" s="5">
+        <f>M2b_MpptRatio!G8</f>
+        <v/>
+      </c>
+      <c r="M8" s="5">
+        <f>SUM(Helpers_MR!C5:C30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>pyranometer_per_ws</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>WB05-INV05</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>WB05</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>PV5</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="5">
+        <f>M2b_MpptRatio!J9</f>
+        <v/>
+      </c>
+      <c r="G9" s="5">
+        <f>M2b_MpptRatio!C9</f>
+        <v/>
+      </c>
+      <c r="H9" s="31">
+        <f>M2b_MpptRatio!D9</f>
+        <v/>
+      </c>
+      <c r="I9" s="31">
+        <f>M2b_MpptRatio!D9</f>
+        <v/>
+      </c>
+      <c r="J9" s="5">
+        <f>SUM(Helpers_MR!Z5:Z30)</f>
+        <v/>
+      </c>
+      <c r="K9" s="5">
+        <f>M2b_MpptRatio!G9</f>
+        <v/>
+      </c>
+      <c r="L9" s="5">
+        <f>M2b_MpptRatio!G9</f>
+        <v/>
+      </c>
+      <c r="M9" s="5">
+        <f>SUM(Helpers_MR!C5:C30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>pyranometer_per_ws</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>WB05-INV05</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>WB05</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>PV6</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="5">
+        <f>M2b_MpptRatio!J10</f>
+        <v/>
+      </c>
+      <c r="G10" s="5">
+        <f>M2b_MpptRatio!C10</f>
+        <v/>
+      </c>
+      <c r="H10" s="31">
+        <f>M2b_MpptRatio!D10</f>
+        <v/>
+      </c>
+      <c r="I10" s="31">
+        <f>M2b_MpptRatio!D10</f>
+        <v/>
+      </c>
+      <c r="J10" s="5">
+        <f>SUM(Helpers_MR!AA5:AA30)</f>
+        <v/>
+      </c>
+      <c r="K10" s="5">
+        <f>M2b_MpptRatio!G10</f>
+        <v/>
+      </c>
+      <c r="L10" s="5">
+        <f>M2b_MpptRatio!G10</f>
+        <v/>
+      </c>
+      <c r="M10" s="5">
+        <f>SUM(Helpers_MR!C5:C30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>pyranometer_per_ws</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>WB05-INV05</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>WB05</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>PV7</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="5">
+        <f>M2b_MpptRatio!J11</f>
+        <v/>
+      </c>
+      <c r="G11" s="5">
+        <f>M2b_MpptRatio!C11</f>
+        <v/>
+      </c>
+      <c r="H11" s="31">
+        <f>M2b_MpptRatio!D11</f>
+        <v/>
+      </c>
+      <c r="I11" s="31">
+        <f>M2b_MpptRatio!D11</f>
+        <v/>
+      </c>
+      <c r="J11" s="5">
+        <f>SUM(Helpers_MR!AB5:AB30)</f>
+        <v/>
+      </c>
+      <c r="K11" s="5">
+        <f>M2b_MpptRatio!G11</f>
+        <v/>
+      </c>
+      <c r="L11" s="5">
+        <f>M2b_MpptRatio!G11</f>
+        <v/>
+      </c>
+      <c r="M11" s="5">
+        <f>SUM(Helpers_MR!C5:C30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>pyranometer_per_ws</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>WB05-INV05</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>WB05</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>PV8</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="5">
+        <f>M2b_MpptRatio!J12</f>
+        <v/>
+      </c>
+      <c r="G12" s="5">
+        <f>M2b_MpptRatio!C12</f>
+        <v/>
+      </c>
+      <c r="H12" s="31">
+        <f>M2b_MpptRatio!D12</f>
+        <v/>
+      </c>
+      <c r="I12" s="31">
+        <f>M2b_MpptRatio!D12</f>
+        <v/>
+      </c>
+      <c r="J12" s="5">
+        <f>SUM(Helpers_MR!AC5:AC30)</f>
+        <v/>
+      </c>
+      <c r="K12" s="5">
+        <f>M2b_MpptRatio!G12</f>
+        <v/>
+      </c>
+      <c r="L12" s="5">
+        <f>M2b_MpptRatio!G12</f>
+        <v/>
+      </c>
+      <c r="M12" s="5">
+        <f>SUM(Helpers_MR!C5:C30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>pyranometer_per_ws</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>WB05-INV05</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>WB05</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>PV9</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="5">
+        <f>M2b_MpptRatio!J13</f>
+        <v/>
+      </c>
+      <c r="G13" s="5">
+        <f>M2b_MpptRatio!C13</f>
+        <v/>
+      </c>
+      <c r="H13" s="31">
+        <f>M2b_MpptRatio!D13</f>
+        <v/>
+      </c>
+      <c r="I13" s="31">
+        <f>M2b_MpptRatio!D13</f>
+        <v/>
+      </c>
+      <c r="J13" s="5">
+        <f>SUM(Helpers_MR!AD5:AD30)</f>
+        <v/>
+      </c>
+      <c r="K13" s="5">
+        <f>M2b_MpptRatio!G13</f>
+        <v/>
+      </c>
+      <c r="L13" s="5">
+        <f>M2b_MpptRatio!G13</f>
+        <v/>
+      </c>
+      <c r="M13" s="5">
+        <f>SUM(Helpers_MR!C5:C30)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F5:F13">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"mppt_partner_underperform"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="4">
+      <formula>"NORMAL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="8">
+      <formula>"EMPTY"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
